--- a/VerveStacks_FRA_grids_syn_5/vt_vervestacks_FRA_v1.xlsx
+++ b/VerveStacks_FRA_grids_syn_5/vt_vervestacks_FRA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_syn_5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{28281CCE-8179-47A4-BA30-EDD69CFCC2FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3786E0A6-C7C1-4294-BDA5-9AB29652393F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{F1C076AF-86AE-4887-9CB0-C06C769FB836}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{DB2274F7-A0AE-4B07-8709-B3A0045518DC}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -1340,22 +1340,22 @@
     <t>ele</t>
   </si>
   <si>
+    <t>Aggregated Plant -- operating</t>
+  </si>
+  <si>
+    <t>GW</t>
+  </si>
+  <si>
+    <t>TWh</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
     <t>Aggregated Plant -- construction</t>
-  </si>
-  <si>
-    <t>GW</t>
-  </si>
-  <si>
-    <t>TWh</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>Aggregated Plant -- operating</t>
   </si>
   <si>
     <t>Isséane Waste-To-Energy power station_1 -- operating</t>
@@ -3598,7 +3598,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D690C85F-FACA-48F0-8E65-ED5DFA9423A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B221316D-EAA5-410D-9748-68299CB8283B}">
   <dimension ref="B9:T115"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9552,7 +9552,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E83CDF34-83D8-4142-AAA1-F8EBA7AD84D3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E37F7E22-BCD3-4068-BB9E-87BDA95E7C12}">
   <dimension ref="B9:T130"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15728,7 +15728,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C857E269-68F1-49AC-A8DB-ADE0632B1A71}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF9E741A-A90B-47A3-99FB-72D974B6F4AB}">
   <dimension ref="B9:T875"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -16258,7 +16258,7 @@
         <v>24</v>
       </c>
       <c r="P19" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q19" t="s">
         <v>434</v>
@@ -20043,7 +20043,7 @@
         <v>101</v>
       </c>
       <c r="P92" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q92" t="s">
         <v>434</v>
@@ -22746,7 +22746,7 @@
         <v>154</v>
       </c>
       <c r="P143" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q143" t="s">
         <v>434</v>
@@ -25660,7 +25660,7 @@
         <v>210</v>
       </c>
       <c r="P199" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q199" t="s">
         <v>434</v>
@@ -25713,7 +25713,7 @@
         <v>211</v>
       </c>
       <c r="P200" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q200" t="s">
         <v>434</v>
@@ -30695,7 +30695,7 @@
         <v>311</v>
       </c>
       <c r="P294" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q294" t="s">
         <v>434</v>
@@ -30748,7 +30748,7 @@
         <v>313</v>
       </c>
       <c r="P295" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q295" t="s">
         <v>434</v>
@@ -30801,7 +30801,7 @@
         <v>315</v>
       </c>
       <c r="P296" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q296" t="s">
         <v>434</v>
@@ -30836,7 +30836,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L297">
-        <v>0.17165578681961038</v>
+        <v>0.17165578681961036</v>
       </c>
       <c r="N297" t="s">
         <v>432</v>
@@ -30845,7 +30845,7 @@
         <v>315</v>
       </c>
       <c r="P297" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="Q297" t="s">
         <v>434</v>
@@ -30880,7 +30880,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L298">
-        <v>0.17165578681961038</v>
+        <v>0.17165578681961036</v>
       </c>
       <c r="N298" t="s">
         <v>432</v>
@@ -30889,7 +30889,7 @@
         <v>317</v>
       </c>
       <c r="P298" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q298" t="s">
         <v>434</v>
@@ -30924,7 +30924,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L299">
-        <v>0.17165578681961038</v>
+        <v>0.17165578681961036</v>
       </c>
       <c r="N299" t="s">
         <v>432</v>
@@ -30933,7 +30933,7 @@
         <v>319</v>
       </c>
       <c r="P299" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q299" t="s">
         <v>434</v>
@@ -31101,7 +31101,7 @@
         <v>322</v>
       </c>
       <c r="P302" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q302" t="s">
         <v>434</v>
@@ -31157,7 +31157,7 @@
         <v>324</v>
       </c>
       <c r="P303" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q303" t="s">
         <v>434</v>
@@ -31213,7 +31213,7 @@
         <v>326</v>
       </c>
       <c r="P304" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q304" t="s">
         <v>434</v>
@@ -31269,7 +31269,7 @@
         <v>328</v>
       </c>
       <c r="P305" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q305" t="s">
         <v>434</v>
@@ -31437,7 +31437,7 @@
         <v>332</v>
       </c>
       <c r="P308" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q308" t="s">
         <v>434</v>
@@ -31493,7 +31493,7 @@
         <v>334</v>
       </c>
       <c r="P309" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q309" t="s">
         <v>434</v>
@@ -31549,7 +31549,7 @@
         <v>336</v>
       </c>
       <c r="P310" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q310" t="s">
         <v>434</v>
@@ -31605,7 +31605,7 @@
         <v>338</v>
       </c>
       <c r="P311" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q311" t="s">
         <v>434</v>
@@ -31661,7 +31661,7 @@
         <v>340</v>
       </c>
       <c r="P312" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q312" t="s">
         <v>434</v>
@@ -31941,7 +31941,7 @@
         <v>346</v>
       </c>
       <c r="P317" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q317" t="s">
         <v>434</v>
@@ -31997,7 +31997,7 @@
         <v>348</v>
       </c>
       <c r="P318" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q318" t="s">
         <v>434</v>
@@ -32053,7 +32053,7 @@
         <v>350</v>
       </c>
       <c r="P319" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q319" t="s">
         <v>434</v>
@@ -32109,7 +32109,7 @@
         <v>352</v>
       </c>
       <c r="P320" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q320" t="s">
         <v>434</v>
@@ -32277,7 +32277,7 @@
         <v>356</v>
       </c>
       <c r="P323" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q323" t="s">
         <v>434</v>
@@ -32445,7 +32445,7 @@
         <v>360</v>
       </c>
       <c r="P326" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q326" t="s">
         <v>434</v>
@@ -32501,7 +32501,7 @@
         <v>360</v>
       </c>
       <c r="P327" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="Q327" t="s">
         <v>434</v>
@@ -32557,7 +32557,7 @@
         <v>362</v>
       </c>
       <c r="P328" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q328" t="s">
         <v>434</v>
@@ -32613,7 +32613,7 @@
         <v>363</v>
       </c>
       <c r="P329" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q329" t="s">
         <v>434</v>
@@ -32669,7 +32669,7 @@
         <v>364</v>
       </c>
       <c r="P330" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q330" t="s">
         <v>434</v>
@@ -32781,7 +32781,7 @@
         <v>367</v>
       </c>
       <c r="P332" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q332" t="s">
         <v>434</v>
@@ -32837,7 +32837,7 @@
         <v>368</v>
       </c>
       <c r="P333" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q333" t="s">
         <v>434</v>
@@ -32893,7 +32893,7 @@
         <v>371</v>
       </c>
       <c r="P334" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q334" t="s">
         <v>434</v>
@@ -32949,7 +32949,7 @@
         <v>373</v>
       </c>
       <c r="P335" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q335" t="s">
         <v>434</v>
@@ -33453,7 +33453,7 @@
         <v>384</v>
       </c>
       <c r="P344" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q344" t="s">
         <v>434</v>
@@ -33509,7 +33509,7 @@
         <v>387</v>
       </c>
       <c r="P345" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q345" t="s">
         <v>434</v>
@@ -33677,7 +33677,7 @@
         <v>391</v>
       </c>
       <c r="P348" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q348" t="s">
         <v>434</v>
@@ -33733,7 +33733,7 @@
         <v>393</v>
       </c>
       <c r="P349" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q349" t="s">
         <v>434</v>
@@ -33789,7 +33789,7 @@
         <v>395</v>
       </c>
       <c r="P350" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q350" t="s">
         <v>434</v>
@@ -33845,7 +33845,7 @@
         <v>397</v>
       </c>
       <c r="P351" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q351" t="s">
         <v>434</v>
@@ -33901,7 +33901,7 @@
         <v>399</v>
       </c>
       <c r="P352" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q352" t="s">
         <v>434</v>
@@ -33957,7 +33957,7 @@
         <v>401</v>
       </c>
       <c r="P353" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q353" t="s">
         <v>434</v>
@@ -34013,7 +34013,7 @@
         <v>401</v>
       </c>
       <c r="P354" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="Q354" t="s">
         <v>434</v>
@@ -34181,7 +34181,7 @@
         <v>405</v>
       </c>
       <c r="P357" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q357" t="s">
         <v>434</v>
@@ -34237,7 +34237,7 @@
         <v>405</v>
       </c>
       <c r="P358" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="Q358" t="s">
         <v>434</v>
@@ -34293,7 +34293,7 @@
         <v>407</v>
       </c>
       <c r="P359" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q359" t="s">
         <v>434</v>
@@ -34349,7 +34349,7 @@
         <v>407</v>
       </c>
       <c r="P360" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="Q360" t="s">
         <v>434</v>
@@ -34517,7 +34517,7 @@
         <v>411</v>
       </c>
       <c r="P363" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q363" t="s">
         <v>434</v>
@@ -34573,7 +34573,7 @@
         <v>413</v>
       </c>
       <c r="P364" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="Q364" t="s">
         <v>434</v>
@@ -34629,7 +34629,7 @@
         <v>413</v>
       </c>
       <c r="P365" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q365" t="s">
         <v>434</v>
@@ -34685,7 +34685,7 @@
         <v>415</v>
       </c>
       <c r="P366" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q366" t="s">
         <v>434</v>
@@ -34853,7 +34853,7 @@
         <v>419</v>
       </c>
       <c r="P369" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="Q369" t="s">
         <v>434</v>
@@ -34909,7 +34909,7 @@
         <v>419</v>
       </c>
       <c r="P370" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q370" t="s">
         <v>434</v>
@@ -34965,7 +34965,7 @@
         <v>421</v>
       </c>
       <c r="P371" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q371" t="s">
         <v>434</v>
@@ -35021,7 +35021,7 @@
         <v>423</v>
       </c>
       <c r="P372" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q372" t="s">
         <v>434</v>
@@ -52611,7 +52611,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B29F097A-CA30-4DB0-A719-8C0A1D55E72B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38F060CF-15F5-4A07-8086-28512055D69D}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_FRA_grids_syn_5/vt_vervestacks_FRA_v1.xlsx
+++ b/VerveStacks_FRA_grids_syn_5/vt_vervestacks_FRA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_syn_5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3786E0A6-C7C1-4294-BDA5-9AB29652393F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5792703B-CC5F-48A2-871A-159432EB0A50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{DB2274F7-A0AE-4B07-8709-B3A0045518DC}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{66973594-E3E7-46E7-87C9-5BC9496D2DF8}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -3598,7 +3598,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B221316D-EAA5-410D-9748-68299CB8283B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79A2655F-D1ED-4ADD-AB53-FB4DE33107E4}">
   <dimension ref="B9:T115"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9552,7 +9552,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E37F7E22-BCD3-4068-BB9E-87BDA95E7C12}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68A7AEBF-54F4-4310-95A8-3DB9ED296584}">
   <dimension ref="B9:T130"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15728,7 +15728,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF9E741A-A90B-47A3-99FB-72D974B6F4AB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52A9C105-AD88-46C8-ABEB-EE2E65AF9093}">
   <dimension ref="B9:T875"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -30836,7 +30836,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L297">
-        <v>0.17165578681961036</v>
+        <v>0.17165578681961033</v>
       </c>
       <c r="N297" t="s">
         <v>432</v>
@@ -30880,7 +30880,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L298">
-        <v>0.17165578681961036</v>
+        <v>0.17165578681961033</v>
       </c>
       <c r="N298" t="s">
         <v>432</v>
@@ -30924,7 +30924,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L299">
-        <v>0.17165578681961036</v>
+        <v>0.17165578681961033</v>
       </c>
       <c r="N299" t="s">
         <v>432</v>
@@ -30989,7 +30989,7 @@
         <v>321</v>
       </c>
       <c r="P300" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q300" t="s">
         <v>434</v>
@@ -31045,7 +31045,7 @@
         <v>321</v>
       </c>
       <c r="P301" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="Q301" t="s">
         <v>434</v>
@@ -32165,7 +32165,7 @@
         <v>354</v>
       </c>
       <c r="P321" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q321" t="s">
         <v>434</v>
@@ -32221,7 +32221,7 @@
         <v>354</v>
       </c>
       <c r="P322" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="Q322" t="s">
         <v>434</v>
@@ -33005,7 +33005,7 @@
         <v>375</v>
       </c>
       <c r="P336" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="Q336" t="s">
         <v>434</v>
@@ -33061,7 +33061,7 @@
         <v>375</v>
       </c>
       <c r="P337" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q337" t="s">
         <v>434</v>
@@ -33565,7 +33565,7 @@
         <v>389</v>
       </c>
       <c r="P346" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q346" t="s">
         <v>434</v>
@@ -33621,7 +33621,7 @@
         <v>389</v>
       </c>
       <c r="P347" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="Q347" t="s">
         <v>434</v>
@@ -34069,7 +34069,7 @@
         <v>403</v>
       </c>
       <c r="P355" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="Q355" t="s">
         <v>434</v>
@@ -34125,7 +34125,7 @@
         <v>403</v>
       </c>
       <c r="P356" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q356" t="s">
         <v>434</v>
@@ -34293,7 +34293,7 @@
         <v>407</v>
       </c>
       <c r="P359" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="Q359" t="s">
         <v>434</v>
@@ -34349,7 +34349,7 @@
         <v>407</v>
       </c>
       <c r="P360" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q360" t="s">
         <v>434</v>
@@ -34405,7 +34405,7 @@
         <v>409</v>
       </c>
       <c r="P361" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q361" t="s">
         <v>434</v>
@@ -34461,7 +34461,7 @@
         <v>409</v>
       </c>
       <c r="P362" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="Q362" t="s">
         <v>434</v>
@@ -34573,7 +34573,7 @@
         <v>413</v>
       </c>
       <c r="P364" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q364" t="s">
         <v>434</v>
@@ -34629,7 +34629,7 @@
         <v>413</v>
       </c>
       <c r="P365" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="Q365" t="s">
         <v>434</v>
@@ -34741,7 +34741,7 @@
         <v>417</v>
       </c>
       <c r="P367" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="Q367" t="s">
         <v>434</v>
@@ -34797,7 +34797,7 @@
         <v>417</v>
       </c>
       <c r="P368" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q368" t="s">
         <v>434</v>
@@ -44086,7 +44086,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L631">
-        <v>0.48643306464952113</v>
+        <v>0.48643306464952119</v>
       </c>
     </row>
     <row r="632" spans="2:12" x14ac:dyDescent="0.45">
@@ -44109,7 +44109,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L632">
-        <v>0.48643306464952113</v>
+        <v>0.48643306464952119</v>
       </c>
     </row>
     <row r="633" spans="2:12" x14ac:dyDescent="0.45">
@@ -44132,7 +44132,7 @@
         <v>0.33122999999999997</v>
       </c>
       <c r="L633">
-        <v>0.48643306464952113</v>
+        <v>0.48643306464952119</v>
       </c>
     </row>
     <row r="634" spans="2:12" x14ac:dyDescent="0.45">
@@ -52611,7 +52611,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38F060CF-15F5-4A07-8086-28512055D69D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69E80768-FCEE-40B0-90DF-6FAA7F1747B8}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_FRA_grids_syn_5/vt_vervestacks_FRA_v1.xlsx
+++ b/VerveStacks_FRA_grids_syn_5/vt_vervestacks_FRA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_syn_5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5792703B-CC5F-48A2-871A-159432EB0A50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8FDB1C97-4E18-40BA-ACA7-68CFEDA7DB87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{66973594-E3E7-46E7-87C9-5BC9496D2DF8}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{0A2D2DBA-76B1-49A5-B29F-07440C9376AA}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -3598,7 +3598,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79A2655F-D1ED-4ADD-AB53-FB4DE33107E4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98133229-CCC6-4A9B-B51A-1552AAAD123F}">
   <dimension ref="B9:T115"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3733,7 +3733,7 @@
         <v>19</v>
       </c>
       <c r="E12">
-        <v>8.2569014400000001E-2</v>
+        <v>0.12083270400000001</v>
       </c>
       <c r="F12">
         <v>3583</v>
@@ -3789,7 +3789,7 @@
         <v>29</v>
       </c>
       <c r="E13">
-        <v>8.2569014400000001E-2</v>
+        <v>0.12083270400000001</v>
       </c>
       <c r="F13">
         <v>3583</v>
@@ -3845,19 +3845,19 @@
         <v>19</v>
       </c>
       <c r="E14">
-        <v>0.20515333999999999</v>
+        <v>0.33007380000000003</v>
       </c>
       <c r="F14">
-        <v>2445</v>
+        <v>1967</v>
       </c>
       <c r="G14">
-        <v>30.4</v>
+        <v>25.2</v>
       </c>
       <c r="H14">
-        <v>3.52</v>
+        <v>2.73</v>
       </c>
       <c r="I14">
-        <v>0.72770000000000001</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J14" t="s">
         <v>30</v>
@@ -3901,19 +3901,19 @@
         <v>19</v>
       </c>
       <c r="E15">
-        <v>0.20515333999999999</v>
+        <v>0.33007380000000003</v>
       </c>
       <c r="F15">
-        <v>2445</v>
+        <v>1967</v>
       </c>
       <c r="G15">
-        <v>30.4</v>
+        <v>25.2</v>
       </c>
       <c r="H15">
-        <v>3.52</v>
+        <v>2.73</v>
       </c>
       <c r="I15">
-        <v>0.72770000000000001</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J15" t="s">
         <v>31</v>
@@ -3957,19 +3957,19 @@
         <v>29</v>
       </c>
       <c r="E16">
-        <v>0.20515333999999999</v>
+        <v>0.33007379999999997</v>
       </c>
       <c r="F16">
-        <v>2445</v>
+        <v>1967</v>
       </c>
       <c r="G16">
-        <v>30.4</v>
+        <v>25.2</v>
       </c>
       <c r="H16">
-        <v>3.52</v>
+        <v>2.73</v>
       </c>
       <c r="I16">
-        <v>0.72770000000000001</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J16" t="s">
         <v>32</v>
@@ -4013,7 +4013,7 @@
         <v>16</v>
       </c>
       <c r="E17">
-        <v>0.38429300000000005</v>
+        <v>0.5483205000000001</v>
       </c>
       <c r="F17">
         <v>1365</v>
@@ -4069,7 +4069,7 @@
         <v>16</v>
       </c>
       <c r="E18">
-        <v>0.38429300000000005</v>
+        <v>0.5483205000000001</v>
       </c>
       <c r="F18">
         <v>1365</v>
@@ -4125,7 +4125,7 @@
         <v>21</v>
       </c>
       <c r="E19">
-        <v>0.42863449999999986</v>
+        <v>0.61158824999999983</v>
       </c>
       <c r="F19">
         <v>1365</v>
@@ -4181,7 +4181,7 @@
         <v>29</v>
       </c>
       <c r="E20">
-        <v>0.42863449999999992</v>
+        <v>0.61158824999999983</v>
       </c>
       <c r="F20">
         <v>1365</v>
@@ -4237,7 +4237,7 @@
         <v>16</v>
       </c>
       <c r="E21">
-        <v>0.42863449999999992</v>
+        <v>0.61158824999999983</v>
       </c>
       <c r="F21">
         <v>1365</v>
@@ -4293,7 +4293,7 @@
         <v>21</v>
       </c>
       <c r="E22">
-        <v>0.40276862499999999</v>
+        <v>0.57468206249999987</v>
       </c>
       <c r="F22">
         <v>1365</v>
@@ -4349,7 +4349,7 @@
         <v>29</v>
       </c>
       <c r="E23">
-        <v>0.42863449999999992</v>
+        <v>0.61158824999999983</v>
       </c>
       <c r="F23">
         <v>1365</v>
@@ -4405,7 +4405,7 @@
         <v>21</v>
       </c>
       <c r="E24">
-        <v>0.40276862499999999</v>
+        <v>0.57468206250000009</v>
       </c>
       <c r="F24">
         <v>1365</v>
@@ -4461,7 +4461,7 @@
         <v>16</v>
       </c>
       <c r="E25">
-        <v>0.40276862499999999</v>
+        <v>0.57468206249999998</v>
       </c>
       <c r="F25">
         <v>1365</v>
@@ -4517,7 +4517,7 @@
         <v>16</v>
       </c>
       <c r="E26">
-        <v>0.40276862499999999</v>
+        <v>0.57468206249999998</v>
       </c>
       <c r="F26">
         <v>1365</v>
@@ -4573,7 +4573,7 @@
         <v>29</v>
       </c>
       <c r="E27">
-        <v>0.40276862499999999</v>
+        <v>0.57468206249999998</v>
       </c>
       <c r="F27">
         <v>1365</v>
@@ -4629,7 +4629,7 @@
         <v>29</v>
       </c>
       <c r="E28">
-        <v>0.40276862499999999</v>
+        <v>0.57468206249999998</v>
       </c>
       <c r="F28">
         <v>1365</v>
@@ -4685,7 +4685,7 @@
         <v>21</v>
       </c>
       <c r="E29">
-        <v>0.42863449999999992</v>
+        <v>0.61158824999999983</v>
       </c>
       <c r="F29">
         <v>1365</v>
@@ -4741,7 +4741,7 @@
         <v>21</v>
       </c>
       <c r="E30">
-        <v>0.42863449999999992</v>
+        <v>0.61158824999999983</v>
       </c>
       <c r="F30">
         <v>1365</v>
@@ -4797,7 +4797,7 @@
         <v>19</v>
       </c>
       <c r="E31">
-        <v>0.40276862499999999</v>
+        <v>0.57468206249999998</v>
       </c>
       <c r="F31">
         <v>1365</v>
@@ -4853,7 +4853,7 @@
         <v>16</v>
       </c>
       <c r="E32">
-        <v>0.40276862499999999</v>
+        <v>0.57468206249999998</v>
       </c>
       <c r="F32">
         <v>1365</v>
@@ -4909,7 +4909,7 @@
         <v>16</v>
       </c>
       <c r="E33">
-        <v>0.36951250000000002</v>
+        <v>0.52723125000000004</v>
       </c>
       <c r="F33">
         <v>1365</v>
@@ -4965,7 +4965,7 @@
         <v>19</v>
       </c>
       <c r="E34">
-        <v>0.44341499999999995</v>
+        <v>0.63267750000000011</v>
       </c>
       <c r="F34">
         <v>1365</v>
@@ -5021,7 +5021,7 @@
         <v>16</v>
       </c>
       <c r="E35">
-        <v>0.19584162500000005</v>
+        <v>0.27943256250000004</v>
       </c>
       <c r="F35">
         <v>1365</v>
@@ -5077,7 +5077,7 @@
         <v>16</v>
       </c>
       <c r="E36">
-        <v>0.21431724999999996</v>
+        <v>0.30579412499999992</v>
       </c>
       <c r="F36">
         <v>1365</v>
@@ -5133,7 +5133,7 @@
         <v>16</v>
       </c>
       <c r="E37">
-        <v>0.21431724999999993</v>
+        <v>0.30579412499999992</v>
       </c>
       <c r="F37">
         <v>1365</v>
@@ -5189,7 +5189,7 @@
         <v>16</v>
       </c>
       <c r="E38">
-        <v>0.21431724999999993</v>
+        <v>0.30579412499999992</v>
       </c>
       <c r="F38">
         <v>1365</v>
@@ -5245,7 +5245,7 @@
         <v>21</v>
       </c>
       <c r="E39">
-        <v>0.20692700000000003</v>
+        <v>0.2952495</v>
       </c>
       <c r="F39">
         <v>1365</v>
@@ -5301,7 +5301,7 @@
         <v>21</v>
       </c>
       <c r="E40">
-        <v>0.16258549999999999</v>
+        <v>0.23198174999999996</v>
       </c>
       <c r="F40">
         <v>1365</v>
@@ -5357,7 +5357,7 @@
         <v>21</v>
       </c>
       <c r="E41">
-        <v>0.16258549999999999</v>
+        <v>0.23198174999999996</v>
       </c>
       <c r="F41">
         <v>1365</v>
@@ -5413,7 +5413,7 @@
         <v>21</v>
       </c>
       <c r="E42">
-        <v>0.14780500000000002</v>
+        <v>0.21089250000000001</v>
       </c>
       <c r="F42">
         <v>1365</v>
@@ -5469,7 +5469,7 @@
         <v>29</v>
       </c>
       <c r="E43">
-        <v>0.20692700000000003</v>
+        <v>0.2952495</v>
       </c>
       <c r="F43">
         <v>1365</v>
@@ -5525,7 +5525,7 @@
         <v>16</v>
       </c>
       <c r="E44">
-        <v>0.21431724999999996</v>
+        <v>0.30579412499999992</v>
       </c>
       <c r="F44">
         <v>1365</v>
@@ -5581,7 +5581,7 @@
         <v>16</v>
       </c>
       <c r="E45">
-        <v>0.20692700000000003</v>
+        <v>0.2952495</v>
       </c>
       <c r="F45">
         <v>1365</v>
@@ -5637,7 +5637,7 @@
         <v>29</v>
       </c>
       <c r="E46">
-        <v>0.188451375</v>
+        <v>0.26888793749999995</v>
       </c>
       <c r="F46">
         <v>1365</v>
@@ -5693,7 +5693,7 @@
         <v>19</v>
       </c>
       <c r="E47">
-        <v>0.188451375</v>
+        <v>0.26888793749999995</v>
       </c>
       <c r="F47">
         <v>1365</v>
@@ -5749,7 +5749,7 @@
         <v>16</v>
       </c>
       <c r="E48">
-        <v>0.18845137499999998</v>
+        <v>0.26888793749999995</v>
       </c>
       <c r="F48">
         <v>1365</v>
@@ -5805,7 +5805,7 @@
         <v>16</v>
       </c>
       <c r="E49">
-        <v>0.20692700000000003</v>
+        <v>0.2952495</v>
       </c>
       <c r="F49">
         <v>1365</v>
@@ -5861,7 +5861,7 @@
         <v>21</v>
       </c>
       <c r="E50">
-        <v>0.18845137499999998</v>
+        <v>0.26888793749999995</v>
       </c>
       <c r="F50">
         <v>1365</v>
@@ -5917,7 +5917,7 @@
         <v>16</v>
       </c>
       <c r="E51">
-        <v>0.188451375</v>
+        <v>0.26888793749999995</v>
       </c>
       <c r="F51">
         <v>1365</v>
@@ -5973,7 +5973,7 @@
         <v>21</v>
       </c>
       <c r="E52">
-        <v>0.188451375</v>
+        <v>0.26888793749999995</v>
       </c>
       <c r="F52">
         <v>1365</v>
@@ -6029,7 +6029,7 @@
         <v>16</v>
       </c>
       <c r="E53">
-        <v>0.20692700000000006</v>
+        <v>0.2952495</v>
       </c>
       <c r="F53">
         <v>1365</v>
@@ -6085,7 +6085,7 @@
         <v>16</v>
       </c>
       <c r="E54">
-        <v>0.22170749999999997</v>
+        <v>0.31633874999999995</v>
       </c>
       <c r="F54">
         <v>1365</v>
@@ -6141,7 +6141,7 @@
         <v>16</v>
       </c>
       <c r="E55">
-        <v>0.22170749999999997</v>
+        <v>0.31633874999999995</v>
       </c>
       <c r="F55">
         <v>1365</v>
@@ -6197,7 +6197,7 @@
         <v>29</v>
       </c>
       <c r="E56">
-        <v>0.22170749999999997</v>
+        <v>0.31633874999999995</v>
       </c>
       <c r="F56">
         <v>1365</v>
@@ -6253,7 +6253,7 @@
         <v>29</v>
       </c>
       <c r="E57">
-        <v>0.22170749999999997</v>
+        <v>0.31633874999999995</v>
       </c>
       <c r="F57">
         <v>1365</v>
@@ -6309,7 +6309,7 @@
         <v>29</v>
       </c>
       <c r="E58">
-        <v>0.20692700000000006</v>
+        <v>0.2952495</v>
       </c>
       <c r="F58">
         <v>1365</v>
@@ -6365,7 +6365,7 @@
         <v>21</v>
       </c>
       <c r="E59">
-        <v>0.22170749999999997</v>
+        <v>0.31633874999999995</v>
       </c>
       <c r="F59">
         <v>1365</v>
@@ -6421,7 +6421,7 @@
         <v>21</v>
       </c>
       <c r="E60">
-        <v>0.188451375</v>
+        <v>0.26888793749999995</v>
       </c>
       <c r="F60">
         <v>1365</v>
@@ -6477,7 +6477,7 @@
         <v>21</v>
       </c>
       <c r="E61">
-        <v>0.188451375</v>
+        <v>0.26888793749999995</v>
       </c>
       <c r="F61">
         <v>1365</v>
@@ -6533,7 +6533,7 @@
         <v>16</v>
       </c>
       <c r="E62">
-        <v>0.16258549999999999</v>
+        <v>0.23198174999999996</v>
       </c>
       <c r="F62">
         <v>1365</v>
@@ -6589,7 +6589,7 @@
         <v>19</v>
       </c>
       <c r="E63">
-        <v>0.23765752499999998</v>
+        <v>0.33909671250000012</v>
       </c>
       <c r="F63">
         <v>1365</v>
@@ -6645,7 +6645,7 @@
         <v>21</v>
       </c>
       <c r="E64">
-        <v>0.23765752499999998</v>
+        <v>0.33909671250000001</v>
       </c>
       <c r="F64">
         <v>1365</v>
@@ -6701,7 +6701,7 @@
         <v>16</v>
       </c>
       <c r="E65">
-        <v>0.23765752499999998</v>
+        <v>0.33909671250000001</v>
       </c>
       <c r="F65">
         <v>1365</v>
@@ -6757,7 +6757,7 @@
         <v>29</v>
       </c>
       <c r="E66">
-        <v>0.23765752499999998</v>
+        <v>0.33909671250000001</v>
       </c>
       <c r="F66">
         <v>1365</v>
@@ -6813,7 +6813,7 @@
         <v>85</v>
       </c>
       <c r="E67">
-        <v>0.23765752499999998</v>
+        <v>0.33909671250000001</v>
       </c>
       <c r="F67">
         <v>1365</v>
@@ -6869,7 +6869,7 @@
         <v>29</v>
       </c>
       <c r="E68">
-        <v>0.26235387499999996</v>
+        <v>0.37433418749999992</v>
       </c>
       <c r="F68">
         <v>1365</v>
@@ -6925,7 +6925,7 @@
         <v>29</v>
       </c>
       <c r="E69">
-        <v>0.26235387499999996</v>
+        <v>0.37433418749999992</v>
       </c>
       <c r="F69">
         <v>1365</v>
@@ -6981,7 +6981,7 @@
         <v>85</v>
       </c>
       <c r="E70">
-        <v>0.24387825000000002</v>
+        <v>0.34797262500000004</v>
       </c>
       <c r="F70">
         <v>1365</v>
@@ -7037,7 +7037,7 @@
         <v>85</v>
       </c>
       <c r="E71">
-        <v>0.24387825000000002</v>
+        <v>0.34797262499999992</v>
       </c>
       <c r="F71">
         <v>1365</v>
@@ -7093,7 +7093,7 @@
         <v>85</v>
       </c>
       <c r="E72">
-        <v>0.24387825000000002</v>
+        <v>0.34797262499999992</v>
       </c>
       <c r="F72">
         <v>1365</v>
@@ -7149,7 +7149,7 @@
         <v>21</v>
       </c>
       <c r="E73">
-        <v>0.22170749999999997</v>
+        <v>0.31633874999999995</v>
       </c>
       <c r="F73">
         <v>1365</v>
@@ -7205,7 +7205,7 @@
         <v>21</v>
       </c>
       <c r="E74">
-        <v>0.22170749999999997</v>
+        <v>0.31633874999999995</v>
       </c>
       <c r="F74">
         <v>1365</v>
@@ -7261,7 +7261,7 @@
         <v>21</v>
       </c>
       <c r="E75">
-        <v>0.24757337499999998</v>
+        <v>0.35324493750000002</v>
       </c>
       <c r="F75">
         <v>1365</v>
@@ -7317,7 +7317,7 @@
         <v>21</v>
       </c>
       <c r="E76">
-        <v>0.24757337499999998</v>
+        <v>0.35324493750000002</v>
       </c>
       <c r="F76">
         <v>1365</v>
@@ -7373,7 +7373,7 @@
         <v>21</v>
       </c>
       <c r="E77">
-        <v>0.24387825000000002</v>
+        <v>0.34797262500000004</v>
       </c>
       <c r="F77">
         <v>1365</v>
@@ -7429,7 +7429,7 @@
         <v>21</v>
       </c>
       <c r="E78">
-        <v>0.236488</v>
+        <v>0.33742799999999995</v>
       </c>
       <c r="F78">
         <v>1365</v>
@@ -7485,7 +7485,7 @@
         <v>16</v>
       </c>
       <c r="E79">
-        <v>0.24757337499999998</v>
+        <v>0.35324493750000002</v>
       </c>
       <c r="F79">
         <v>1365</v>
@@ -7541,7 +7541,7 @@
         <v>16</v>
       </c>
       <c r="E80">
-        <v>0.24757337499999998</v>
+        <v>0.35324493750000002</v>
       </c>
       <c r="F80">
         <v>1365</v>
@@ -7597,7 +7597,7 @@
         <v>85</v>
       </c>
       <c r="E81">
-        <v>0.236488</v>
+        <v>0.33742799999999995</v>
       </c>
       <c r="F81">
         <v>1365</v>
@@ -7653,7 +7653,7 @@
         <v>16</v>
       </c>
       <c r="E82">
-        <v>0.24387825000000002</v>
+        <v>0.34797262500000004</v>
       </c>
       <c r="F82">
         <v>1365</v>
@@ -7709,7 +7709,7 @@
         <v>21</v>
       </c>
       <c r="E83">
-        <v>0.35473199999999999</v>
+        <v>0.50614199999999998</v>
       </c>
       <c r="F83">
         <v>1365</v>
@@ -7765,7 +7765,7 @@
         <v>16</v>
       </c>
       <c r="E84">
-        <v>0.36951250000000008</v>
+        <v>0.52723125000000004</v>
       </c>
       <c r="F84">
         <v>1365</v>
@@ -7821,7 +7821,7 @@
         <v>16</v>
       </c>
       <c r="E85">
-        <v>0.36951250000000008</v>
+        <v>0.52723125000000004</v>
       </c>
       <c r="F85">
         <v>1365</v>
@@ -7877,7 +7877,7 @@
         <v>16</v>
       </c>
       <c r="E86">
-        <v>0.36951250000000008</v>
+        <v>0.52723125000000004</v>
       </c>
       <c r="F86">
         <v>1365</v>
@@ -7933,7 +7933,7 @@
         <v>85</v>
       </c>
       <c r="E87">
-        <v>0.36951250000000002</v>
+        <v>0.52723125000000004</v>
       </c>
       <c r="F87">
         <v>1365</v>
@@ -7989,7 +7989,7 @@
         <v>16</v>
       </c>
       <c r="E88">
-        <v>0.20692700000000003</v>
+        <v>0.2952495</v>
       </c>
       <c r="F88">
         <v>1365</v>
@@ -8045,7 +8045,7 @@
         <v>16</v>
       </c>
       <c r="E89">
-        <v>0.188451375</v>
+        <v>0.26888793749999995</v>
       </c>
       <c r="F89">
         <v>1365</v>
@@ -8101,7 +8101,7 @@
         <v>19</v>
       </c>
       <c r="E90">
-        <v>0.21431724999999996</v>
+        <v>0.30579412499999992</v>
       </c>
       <c r="F90">
         <v>1365</v>
@@ -8157,7 +8157,7 @@
         <v>21</v>
       </c>
       <c r="E91">
-        <v>0.19953675000000001</v>
+        <v>0.28470487499999997</v>
       </c>
       <c r="F91">
         <v>1365</v>
@@ -8213,7 +8213,7 @@
         <v>29</v>
       </c>
       <c r="E92">
-        <v>0.21431724999999993</v>
+        <v>0.30579412499999992</v>
       </c>
       <c r="F92">
         <v>1365</v>
@@ -8269,7 +8269,7 @@
         <v>21</v>
       </c>
       <c r="E93">
-        <v>0.19953675000000001</v>
+        <v>0.28470487499999997</v>
       </c>
       <c r="F93">
         <v>1365</v>
@@ -8325,7 +8325,7 @@
         <v>21</v>
       </c>
       <c r="E94">
-        <v>0.18106112499999999</v>
+        <v>0.25834331249999998</v>
       </c>
       <c r="F94">
         <v>1365</v>
@@ -8381,7 +8381,7 @@
         <v>21</v>
       </c>
       <c r="E95">
-        <v>0.18106112499999999</v>
+        <v>0.25834331249999998</v>
       </c>
       <c r="F95">
         <v>1365</v>
@@ -8437,7 +8437,7 @@
         <v>21</v>
       </c>
       <c r="E96">
-        <v>0.18106112499999999</v>
+        <v>0.25834331249999998</v>
       </c>
       <c r="F96">
         <v>1365</v>
@@ -8493,7 +8493,7 @@
         <v>29</v>
       </c>
       <c r="E97">
-        <v>0.177366</v>
+        <v>0.25307099999999999</v>
       </c>
       <c r="F97">
         <v>1365</v>
@@ -8549,7 +8549,7 @@
         <v>29</v>
       </c>
       <c r="E98">
-        <v>0.16258549999999997</v>
+        <v>0.23198174999999996</v>
       </c>
       <c r="F98">
         <v>1365</v>
@@ -8605,7 +8605,7 @@
         <v>19</v>
       </c>
       <c r="E99">
-        <v>0.177366</v>
+        <v>0.25307099999999999</v>
       </c>
       <c r="F99">
         <v>1365</v>
@@ -8661,7 +8661,7 @@
         <v>19</v>
       </c>
       <c r="E100">
-        <v>0.188451375</v>
+        <v>0.26888793749999995</v>
       </c>
       <c r="F100">
         <v>1365</v>
@@ -8717,7 +8717,7 @@
         <v>19</v>
       </c>
       <c r="E101">
-        <v>0.16258549999999997</v>
+        <v>0.23198174999999996</v>
       </c>
       <c r="F101">
         <v>1365</v>
@@ -8773,7 +8773,7 @@
         <v>14</v>
       </c>
       <c r="E102">
-        <v>0.19953675000000001</v>
+        <v>0.28470487499999997</v>
       </c>
       <c r="F102">
         <v>1365</v>
@@ -8829,7 +8829,7 @@
         <v>14</v>
       </c>
       <c r="E103">
-        <v>0.19953675000000001</v>
+        <v>0.28470487499999997</v>
       </c>
       <c r="F103">
         <v>1365</v>
@@ -8885,7 +8885,7 @@
         <v>21</v>
       </c>
       <c r="E104">
-        <v>0.23279287499999998</v>
+        <v>0.33215568750000002</v>
       </c>
       <c r="F104">
         <v>1365</v>
@@ -8941,7 +8941,7 @@
         <v>21</v>
       </c>
       <c r="E105">
-        <v>0.25865874999999999</v>
+        <v>0.36906187499999993</v>
       </c>
       <c r="F105">
         <v>1365</v>
@@ -8997,7 +8997,7 @@
         <v>19</v>
       </c>
       <c r="E106">
-        <v>0.23279287499999998</v>
+        <v>0.33215568750000002</v>
       </c>
       <c r="F106">
         <v>1365</v>
@@ -9053,7 +9053,7 @@
         <v>29</v>
       </c>
       <c r="E107">
-        <v>0.22909774999999999</v>
+        <v>0.32688337500000003</v>
       </c>
       <c r="F107">
         <v>1365</v>
@@ -9109,7 +9109,7 @@
         <v>29</v>
       </c>
       <c r="E108">
-        <v>0.22909774999999999</v>
+        <v>0.32688337500000003</v>
       </c>
       <c r="F108">
         <v>1365</v>
@@ -9165,7 +9165,7 @@
         <v>21</v>
       </c>
       <c r="E109">
-        <v>0.21431724999999996</v>
+        <v>0.30579412499999992</v>
       </c>
       <c r="F109">
         <v>1365</v>
@@ -9221,7 +9221,7 @@
         <v>21</v>
       </c>
       <c r="E110">
-        <v>0.22170749999999997</v>
+        <v>0.31633874999999995</v>
       </c>
       <c r="F110">
         <v>1365</v>
@@ -9277,7 +9277,7 @@
         <v>21</v>
       </c>
       <c r="E111">
-        <v>0.24018312500000005</v>
+        <v>0.3427003125000001</v>
       </c>
       <c r="F111">
         <v>1365</v>
@@ -9333,7 +9333,7 @@
         <v>16</v>
       </c>
       <c r="E112">
-        <v>0.20692700000000003</v>
+        <v>0.2952495</v>
       </c>
       <c r="F112">
         <v>1365</v>
@@ -9389,7 +9389,7 @@
         <v>16</v>
       </c>
       <c r="E113">
-        <v>0.21431725000000001</v>
+        <v>0.30579412499999992</v>
       </c>
       <c r="F113">
         <v>1365</v>
@@ -9445,7 +9445,7 @@
         <v>16</v>
       </c>
       <c r="E114">
-        <v>0.21431724999999996</v>
+        <v>0.30579412499999992</v>
       </c>
       <c r="F114">
         <v>1365</v>
@@ -9501,7 +9501,7 @@
         <v>16</v>
       </c>
       <c r="E115">
-        <v>0.20692700000000003</v>
+        <v>0.2952495</v>
       </c>
       <c r="F115">
         <v>1365</v>
@@ -9552,7 +9552,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68A7AEBF-54F4-4310-95A8-3DB9ED296584}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B9421C6-9EEB-4D79-A536-0AA4D1C4F68B}">
   <dimension ref="B9:T130"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15728,7 +15728,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52A9C105-AD88-46C8-ABEB-EE2E65AF9093}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{968AA02A-CE15-4383-BC39-F94673774035}">
   <dimension ref="B9:T875"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15813,7 +15813,7 @@
         <v>0.06</v>
       </c>
       <c r="G11">
-        <v>0.27027200000000001</v>
+        <v>0.39551999999999998</v>
       </c>
       <c r="H11">
         <v>5197.5</v>
@@ -15866,7 +15866,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
       <c r="G12">
-        <v>0.27027200000000001</v>
+        <v>0.39551999999999998</v>
       </c>
       <c r="H12">
         <v>5197.5</v>
@@ -15919,7 +15919,7 @@
         <v>5.1999999999999998E-2</v>
       </c>
       <c r="G13">
-        <v>0.24493399999999996</v>
+        <v>0.35843999999999993</v>
       </c>
       <c r="H13">
         <v>4427.5</v>
@@ -15972,7 +15972,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
       <c r="G14">
-        <v>0.19425800000000001</v>
+        <v>0.28428000000000003</v>
       </c>
       <c r="H14">
         <v>4427.5</v>
@@ -16025,7 +16025,7 @@
         <v>0.05</v>
       </c>
       <c r="G15">
-        <v>0.236488</v>
+        <v>0.34608000000000005</v>
       </c>
       <c r="H15">
         <v>5197.5</v>
@@ -16078,7 +16078,7 @@
         <v>0.15</v>
       </c>
       <c r="G16">
-        <v>0.22381900000000002</v>
+        <v>0.32754</v>
       </c>
       <c r="H16">
         <v>4427.5</v>
@@ -16131,7 +16131,7 @@
         <v>0.20313807531380754</v>
       </c>
       <c r="G17">
-        <v>0.27871800000000002</v>
+        <v>0.40788000000000008</v>
       </c>
       <c r="H17">
         <v>4427.5</v>
@@ -16184,7 +16184,7 @@
         <v>1.1375732217573222</v>
       </c>
       <c r="G18">
-        <v>0.29560999999999998</v>
+        <v>0.43259999999999998</v>
       </c>
       <c r="H18">
         <v>3850.0000000000009</v>
@@ -16237,7 +16237,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
       <c r="G19">
-        <v>0.21537299999999998</v>
+        <v>0.31517999999999996</v>
       </c>
       <c r="H19">
         <v>5197.5</v>
@@ -16290,7 +16290,7 @@
         <v>0.60128870292887027</v>
       </c>
       <c r="G20">
-        <v>0.29560999999999998</v>
+        <v>0.43260000000000004</v>
       </c>
       <c r="H20">
         <v>3850</v>
@@ -16343,7 +16343,7 @@
         <v>0.39841636077608789</v>
       </c>
       <c r="G21">
-        <v>0.27160859999999998</v>
+        <v>0.397476</v>
       </c>
       <c r="N21" t="s">
         <v>432</v>
@@ -16384,7 +16384,7 @@
         <v>0.20458363922391182</v>
       </c>
       <c r="G22">
-        <v>0.27160859999999998</v>
+        <v>0.397476</v>
       </c>
       <c r="N22" t="s">
         <v>432</v>
@@ -16425,7 +16425,7 @@
         <v>0.63</v>
       </c>
       <c r="G23">
-        <v>0.29560999999999998</v>
+        <v>0.43260000000000004</v>
       </c>
       <c r="H23">
         <v>2200</v>
@@ -16478,7 +16478,7 @@
         <v>0.63</v>
       </c>
       <c r="G24">
-        <v>0.29560999999999998</v>
+        <v>0.43260000000000004</v>
       </c>
       <c r="H24">
         <v>2200</v>
@@ -16531,7 +16531,7 @@
         <v>0.64700000000000002</v>
       </c>
       <c r="G25">
-        <v>0.29560999999999998</v>
+        <v>0.43259999999999998</v>
       </c>
       <c r="H25">
         <v>2200</v>
@@ -16584,7 +16584,7 @@
         <v>0.12</v>
       </c>
       <c r="G26">
-        <v>0.43919200000000003</v>
+        <v>0.6266520000000001</v>
       </c>
       <c r="H26">
         <v>1265</v>
@@ -16637,7 +16637,7 @@
         <v>0.12</v>
       </c>
       <c r="G27">
-        <v>0.43919200000000003</v>
+        <v>0.6266520000000001</v>
       </c>
       <c r="H27">
         <v>1265</v>
@@ -16690,7 +16690,7 @@
         <v>0.40100000000000002</v>
       </c>
       <c r="G28">
-        <v>0.48986799999999986</v>
+        <v>0.69895799999999986</v>
       </c>
       <c r="H28">
         <v>1100</v>
@@ -16743,7 +16743,7 @@
         <v>0.42699999999999999</v>
       </c>
       <c r="G29">
-        <v>0.48986799999999991</v>
+        <v>0.69895799999999986</v>
       </c>
       <c r="H29">
         <v>1100</v>
@@ -16796,7 +16796,7 @@
         <v>0.58499999999999996</v>
       </c>
       <c r="G30">
-        <v>0.48986799999999991</v>
+        <v>0.69895799999999986</v>
       </c>
       <c r="H30">
         <v>1100</v>
@@ -16849,7 +16849,7 @@
         <v>0.45300000000000001</v>
       </c>
       <c r="G31">
-        <v>0.46030699999999997</v>
+        <v>0.65677949999999985</v>
       </c>
       <c r="H31">
         <v>1100</v>
@@ -16902,7 +16902,7 @@
         <v>0.41299999999999998</v>
       </c>
       <c r="G32">
-        <v>0.48986799999999991</v>
+        <v>0.69895799999999986</v>
       </c>
       <c r="H32">
         <v>1100</v>
@@ -16955,7 +16955,7 @@
         <v>0.42799999999999999</v>
       </c>
       <c r="G33">
-        <v>0.46030699999999997</v>
+        <v>0.65677950000000007</v>
       </c>
       <c r="H33">
         <v>1100</v>
@@ -17008,7 +17008,7 @@
         <v>0.40400000000000003</v>
       </c>
       <c r="G34">
-        <v>0.46030699999999997</v>
+        <v>0.65677949999999996</v>
       </c>
       <c r="H34">
         <v>1100</v>
@@ -17061,7 +17061,7 @@
         <v>0.40400000000000003</v>
       </c>
       <c r="G35">
-        <v>0.46030699999999997</v>
+        <v>0.65677949999999996</v>
       </c>
       <c r="H35">
         <v>1100</v>
@@ -17114,7 +17114,7 @@
         <v>0.44</v>
       </c>
       <c r="G36">
-        <v>0.46030699999999997</v>
+        <v>0.65677949999999996</v>
       </c>
       <c r="H36">
         <v>1100</v>
@@ -17167,7 +17167,7 @@
         <v>0.44</v>
       </c>
       <c r="G37">
-        <v>0.46030699999999997</v>
+        <v>0.65677949999999996</v>
       </c>
       <c r="H37">
         <v>1100</v>
@@ -17220,7 +17220,7 @@
         <v>0.499</v>
       </c>
       <c r="G38">
-        <v>0.48986799999999991</v>
+        <v>0.69895799999999986</v>
       </c>
       <c r="H38">
         <v>1100</v>
@@ -17273,7 +17273,7 @@
         <v>0.499</v>
       </c>
       <c r="G39">
-        <v>0.48986799999999991</v>
+        <v>0.69895799999999986</v>
       </c>
       <c r="H39">
         <v>1100</v>
@@ -17326,7 +17326,7 @@
         <v>0.435</v>
       </c>
       <c r="G40">
-        <v>0.46030699999999997</v>
+        <v>0.65677949999999996</v>
       </c>
       <c r="H40">
         <v>1100</v>
@@ -17379,7 +17379,7 @@
         <v>0.45</v>
       </c>
       <c r="G41">
-        <v>0.46030699999999997</v>
+        <v>0.65677949999999996</v>
       </c>
       <c r="H41">
         <v>1100</v>
@@ -17432,7 +17432,7 @@
         <v>0.13200000000000001</v>
       </c>
       <c r="G42">
-        <v>0.42230000000000001</v>
+        <v>0.60255000000000003</v>
       </c>
       <c r="H42">
         <v>1265</v>
@@ -17485,7 +17485,7 @@
         <v>0.44600000000000001</v>
       </c>
       <c r="G43">
-        <v>0.50675999999999999</v>
+        <v>0.72306000000000004</v>
       </c>
       <c r="H43">
         <v>1100</v>
@@ -17538,7 +17538,7 @@
         <v>0.20300000000000001</v>
       </c>
       <c r="G44">
-        <v>0.22381900000000005</v>
+        <v>0.31935150000000001</v>
       </c>
       <c r="H44">
         <v>1012</v>
@@ -17591,7 +17591,7 @@
         <v>0.125</v>
       </c>
       <c r="G45">
-        <v>0.24493399999999996</v>
+        <v>0.34947899999999993</v>
       </c>
       <c r="H45">
         <v>1012</v>
@@ -17644,7 +17644,7 @@
         <v>0.2</v>
       </c>
       <c r="G46">
-        <v>0.24493399999999993</v>
+        <v>0.34947899999999987</v>
       </c>
       <c r="H46">
         <v>1012</v>
@@ -17697,7 +17697,7 @@
         <v>0.2</v>
       </c>
       <c r="G47">
-        <v>0.24493399999999993</v>
+        <v>0.34947899999999987</v>
       </c>
       <c r="H47">
         <v>1012</v>
@@ -17750,7 +17750,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="G48">
-        <v>0.23648800000000003</v>
+        <v>0.33742800000000001</v>
       </c>
       <c r="H48">
         <v>1188</v>
@@ -17803,7 +17803,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
       <c r="G49">
-        <v>0.18581199999999998</v>
+        <v>0.26512199999999997</v>
       </c>
       <c r="H49">
         <v>1188</v>
@@ -17856,7 +17856,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
       <c r="G50">
-        <v>0.18581199999999998</v>
+        <v>0.26512199999999997</v>
       </c>
       <c r="H50">
         <v>1188</v>
@@ -17909,7 +17909,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
       <c r="G51">
-        <v>0.16892000000000001</v>
+        <v>0.24101999999999998</v>
       </c>
       <c r="H51">
         <v>1188</v>
@@ -17962,7 +17962,7 @@
         <v>0.02</v>
       </c>
       <c r="G52">
-        <v>0.23648800000000003</v>
+        <v>0.33742800000000001</v>
       </c>
       <c r="H52">
         <v>1188</v>
@@ -18015,7 +18015,7 @@
         <v>0.128</v>
       </c>
       <c r="G53">
-        <v>0.24493399999999996</v>
+        <v>0.34947899999999993</v>
       </c>
       <c r="H53">
         <v>1012</v>
@@ -18068,7 +18068,7 @@
         <v>4.7E-2</v>
       </c>
       <c r="G54">
-        <v>0.23648800000000003</v>
+        <v>0.33742800000000001</v>
       </c>
       <c r="H54">
         <v>1188</v>
@@ -18121,7 +18121,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="G55">
-        <v>0.21537299999999998</v>
+        <v>0.30730049999999998</v>
       </c>
       <c r="H55">
         <v>1188</v>
@@ -18174,7 +18174,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
       <c r="G56">
-        <v>0.21537299999999998</v>
+        <v>0.30730049999999998</v>
       </c>
       <c r="H56">
         <v>1188</v>
@@ -18227,7 +18227,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
       <c r="G57">
-        <v>0.21537299999999995</v>
+        <v>0.30730049999999998</v>
       </c>
       <c r="H57">
         <v>1188</v>
@@ -18280,7 +18280,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
       <c r="G58">
-        <v>0.236488</v>
+        <v>0.33742800000000001</v>
       </c>
       <c r="H58">
         <v>1188</v>
@@ -18333,7 +18333,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
       <c r="G59">
-        <v>0.21537299999999995</v>
+        <v>0.30730049999999998</v>
       </c>
       <c r="H59">
         <v>1188</v>
@@ -18386,7 +18386,7 @@
         <v>0.03</v>
       </c>
       <c r="G60">
-        <v>0.21537299999999998</v>
+        <v>0.30730049999999998</v>
       </c>
       <c r="H60">
         <v>1188</v>
@@ -18439,7 +18439,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="G61">
-        <v>0.21537299999999998</v>
+        <v>0.30730049999999998</v>
       </c>
       <c r="H61">
         <v>1188</v>
@@ -18492,7 +18492,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
       <c r="G62">
-        <v>0.23648800000000006</v>
+        <v>0.33742800000000001</v>
       </c>
       <c r="H62">
         <v>1188</v>
@@ -18545,7 +18545,7 @@
         <v>0.04</v>
       </c>
       <c r="G63">
-        <v>0.25337999999999999</v>
+        <v>0.36152999999999996</v>
       </c>
       <c r="H63">
         <v>1188</v>
@@ -18598,7 +18598,7 @@
         <v>0.04</v>
       </c>
       <c r="G64">
-        <v>0.25337999999999999</v>
+        <v>0.36152999999999996</v>
       </c>
       <c r="H64">
         <v>1188</v>
@@ -18651,7 +18651,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="G65">
-        <v>0.25337999999999999</v>
+        <v>0.36152999999999996</v>
       </c>
       <c r="H65">
         <v>1188</v>
@@ -18704,7 +18704,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="G66">
-        <v>0.25337999999999999</v>
+        <v>0.36152999999999996</v>
       </c>
       <c r="H66">
         <v>1188</v>
@@ -18757,7 +18757,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
       <c r="G67">
-        <v>0.23648800000000006</v>
+        <v>0.33742800000000001</v>
       </c>
       <c r="H67">
         <v>1188</v>
@@ -18810,7 +18810,7 @@
         <v>2.4500000000000001E-2</v>
       </c>
       <c r="G68">
-        <v>0.25337999999999999</v>
+        <v>0.36152999999999996</v>
       </c>
       <c r="H68">
         <v>1188</v>
@@ -18863,7 +18863,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="G69">
-        <v>0.21537300000000001</v>
+        <v>0.30730049999999998</v>
       </c>
       <c r="H69">
         <v>1188</v>
@@ -18916,7 +18916,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
       <c r="G70">
-        <v>0.21537299999999998</v>
+        <v>0.30730049999999998</v>
       </c>
       <c r="H70">
         <v>1188</v>
@@ -18969,7 +18969,7 @@
         <v>2.4E-2</v>
       </c>
       <c r="G71">
-        <v>0.18581199999999998</v>
+        <v>0.26512199999999997</v>
       </c>
       <c r="H71">
         <v>1188</v>
@@ -19022,7 +19022,7 @@
         <v>0.75747865668823344</v>
       </c>
       <c r="G72">
-        <v>0.27160859999999998</v>
+        <v>0.38753910000000008</v>
       </c>
       <c r="N72" t="s">
         <v>432</v>
@@ -19063,7 +19063,7 @@
         <v>2.3813963614498546</v>
       </c>
       <c r="G73">
-        <v>0.27160859999999998</v>
+        <v>0.38753910000000003</v>
       </c>
       <c r="N73" t="s">
         <v>432</v>
@@ -19104,7 +19104,7 @@
         <v>2.8964818479978529</v>
       </c>
       <c r="G74">
-        <v>0.27160859999999998</v>
+        <v>0.38753910000000003</v>
       </c>
       <c r="N74" t="s">
         <v>432</v>
@@ -19145,7 +19145,7 @@
         <v>2.2224923223709707</v>
       </c>
       <c r="G75">
-        <v>0.27160859999999998</v>
+        <v>0.38753910000000003</v>
       </c>
       <c r="N75" t="s">
         <v>432</v>
@@ -19186,7 +19186,7 @@
         <v>0.11745081149308761</v>
       </c>
       <c r="G76">
-        <v>0.27160859999999998</v>
+        <v>0.38753910000000003</v>
       </c>
       <c r="N76" t="s">
         <v>432</v>
@@ -19227,7 +19227,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="G77">
-        <v>0.29983299999999996</v>
+        <v>0.42781049999999993</v>
       </c>
       <c r="H77">
         <v>1633.5000000000002</v>
@@ -19280,7 +19280,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="G78">
-        <v>0.29983299999999996</v>
+        <v>0.42781049999999993</v>
       </c>
       <c r="H78">
         <v>1633.5000000000002</v>
@@ -19333,7 +19333,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
       <c r="G79">
-        <v>0.27871800000000002</v>
+        <v>0.39768300000000001</v>
       </c>
       <c r="H79">
         <v>1782.0000000000002</v>
@@ -19386,7 +19386,7 @@
         <v>4.36E-2</v>
       </c>
       <c r="G80">
-        <v>0.27871800000000002</v>
+        <v>0.39768299999999995</v>
       </c>
       <c r="H80">
         <v>1782.0000000000002</v>
@@ -19439,7 +19439,7 @@
         <v>4.36E-2</v>
       </c>
       <c r="G81">
-        <v>0.27871800000000002</v>
+        <v>0.39768299999999995</v>
       </c>
       <c r="H81">
         <v>1782.0000000000002</v>
@@ -19492,7 +19492,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="G82">
-        <v>0.25337999999999999</v>
+        <v>0.36152999999999996</v>
       </c>
       <c r="H82">
         <v>1782.0000000000002</v>
@@ -19545,7 +19545,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="G83">
-        <v>0.25337999999999999</v>
+        <v>0.36152999999999996</v>
       </c>
       <c r="H83">
         <v>1782.0000000000002</v>
@@ -19598,7 +19598,7 @@
         <v>2.7E-2</v>
       </c>
       <c r="G84">
-        <v>0.282941</v>
+        <v>0.40370850000000003</v>
       </c>
       <c r="H84">
         <v>1782.0000000000002</v>
@@ -19651,7 +19651,7 @@
         <v>2.7E-2</v>
       </c>
       <c r="G85">
-        <v>0.282941</v>
+        <v>0.40370850000000003</v>
       </c>
       <c r="H85">
         <v>1782.0000000000002</v>
@@ -19704,7 +19704,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
       <c r="G86">
-        <v>0.27871800000000002</v>
+        <v>0.39768300000000001</v>
       </c>
       <c r="H86">
         <v>1518.0000000000002</v>
@@ -19757,7 +19757,7 @@
         <v>3.8399999999999997E-2</v>
       </c>
       <c r="G87">
-        <v>0.27027200000000001</v>
+        <v>0.38563199999999997</v>
       </c>
       <c r="H87">
         <v>1782.0000000000002</v>
@@ -19810,7 +19810,7 @@
         <v>2.4E-2</v>
       </c>
       <c r="G88">
-        <v>0.282941</v>
+        <v>0.40370850000000003</v>
       </c>
       <c r="H88">
         <v>1782.0000000000002</v>
@@ -19863,7 +19863,7 @@
         <v>2.4E-2</v>
       </c>
       <c r="G89">
-        <v>0.282941</v>
+        <v>0.40370850000000003</v>
       </c>
       <c r="H89">
         <v>1782.0000000000002</v>
@@ -19916,7 +19916,7 @@
         <v>2.0899999999999998E-2</v>
       </c>
       <c r="G90">
-        <v>0.27027200000000001</v>
+        <v>0.38563199999999997</v>
       </c>
       <c r="H90">
         <v>1782.0000000000002</v>
@@ -19969,7 +19969,7 @@
         <v>4.87E-2</v>
       </c>
       <c r="G91">
-        <v>0.27871800000000002</v>
+        <v>0.39768300000000001</v>
       </c>
       <c r="H91">
         <v>1782.0000000000005</v>
@@ -29084,7 +29084,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
       <c r="G264">
-        <v>0.40540799999999999</v>
+        <v>0.57844799999999996</v>
       </c>
       <c r="H264">
         <v>1633.5000000000002</v>
@@ -29137,7 +29137,7 @@
         <v>0.2</v>
       </c>
       <c r="G265">
-        <v>0.42230000000000006</v>
+        <v>0.60255000000000003</v>
       </c>
       <c r="H265">
         <v>1391.5</v>
@@ -29190,7 +29190,7 @@
         <v>0.2</v>
       </c>
       <c r="G266">
-        <v>0.42230000000000006</v>
+        <v>0.60255000000000003</v>
       </c>
       <c r="H266">
         <v>1391.5</v>
@@ -29243,7 +29243,7 @@
         <v>0.2</v>
       </c>
       <c r="G267">
-        <v>0.42230000000000006</v>
+        <v>0.60255000000000003</v>
       </c>
       <c r="H267">
         <v>1391.5</v>
@@ -29296,7 +29296,7 @@
         <v>6.0999999999999999E-2</v>
       </c>
       <c r="G268">
-        <v>0.42230000000000001</v>
+        <v>0.60255000000000003</v>
       </c>
       <c r="H268">
         <v>1391.5</v>
@@ -29349,7 +29349,7 @@
         <v>0.125</v>
       </c>
       <c r="G269">
-        <v>0.23648800000000003</v>
+        <v>0.33742800000000001</v>
       </c>
       <c r="H269">
         <v>1138.5</v>
@@ -29402,7 +29402,7 @@
         <v>0.125</v>
       </c>
       <c r="G270">
-        <v>0.21537299999999998</v>
+        <v>0.30730049999999998</v>
       </c>
       <c r="H270">
         <v>1138.5</v>
@@ -29455,7 +29455,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
       <c r="G271">
-        <v>0.24493399999999996</v>
+        <v>0.34947899999999993</v>
       </c>
       <c r="H271">
         <v>1336.5</v>
@@ -29508,7 +29508,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
       <c r="G272">
-        <v>0.22804200000000002</v>
+        <v>0.32537699999999997</v>
       </c>
       <c r="H272">
         <v>1336.5</v>
@@ -29561,7 +29561,7 @@
         <v>0.05</v>
       </c>
       <c r="G273">
-        <v>0.24493399999999993</v>
+        <v>0.34947899999999987</v>
       </c>
       <c r="H273">
         <v>1336.5</v>
@@ -29614,7 +29614,7 @@
         <v>0.04</v>
       </c>
       <c r="G274">
-        <v>0.22804199999999999</v>
+        <v>0.32537699999999997</v>
       </c>
       <c r="H274">
         <v>1336.5</v>
@@ -29667,7 +29667,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G275">
-        <v>0.20692699999999997</v>
+        <v>0.2952495</v>
       </c>
       <c r="H275">
         <v>1336.5</v>
@@ -29720,7 +29720,7 @@
         <v>0.02</v>
       </c>
       <c r="G276">
-        <v>0.206927</v>
+        <v>0.2952495</v>
       </c>
       <c r="H276">
         <v>1336.5</v>
@@ -29773,7 +29773,7 @@
         <v>0.02</v>
       </c>
       <c r="G277">
-        <v>0.206927</v>
+        <v>0.2952495</v>
       </c>
       <c r="H277">
         <v>1336.5</v>
@@ -29826,7 +29826,7 @@
         <v>9.1999999999999998E-2</v>
       </c>
       <c r="G278">
-        <v>0.202704</v>
+        <v>0.28922399999999998</v>
       </c>
       <c r="H278">
         <v>1138.5</v>
@@ -29879,7 +29879,7 @@
         <v>9.1999999999999998E-2</v>
       </c>
       <c r="G279">
-        <v>0.18581199999999995</v>
+        <v>0.26512199999999997</v>
       </c>
       <c r="H279">
         <v>1138.5</v>
@@ -29932,7 +29932,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="G280">
-        <v>0.202704</v>
+        <v>0.28922399999999998</v>
       </c>
       <c r="H280">
         <v>1138.5</v>
@@ -29985,7 +29985,7 @@
         <v>9.1999999999999998E-2</v>
       </c>
       <c r="G281">
-        <v>0.21537299999999998</v>
+        <v>0.30730049999999998</v>
       </c>
       <c r="H281">
         <v>1138.5</v>
@@ -30038,7 +30038,7 @@
         <v>9.1999999999999998E-2</v>
       </c>
       <c r="G282">
-        <v>0.18581199999999995</v>
+        <v>0.26512199999999997</v>
       </c>
       <c r="H282">
         <v>1138.5</v>
@@ -30091,7 +30091,7 @@
         <v>0.04</v>
       </c>
       <c r="G283">
-        <v>0.22804199999999999</v>
+        <v>0.32537699999999997</v>
       </c>
       <c r="H283">
         <v>1336.5</v>
@@ -30144,7 +30144,7 @@
         <v>0.04</v>
       </c>
       <c r="G284">
-        <v>0.22804199999999999</v>
+        <v>0.32537699999999997</v>
       </c>
       <c r="H284">
         <v>1336.5</v>
@@ -30197,7 +30197,7 @@
         <v>0.13300000000000001</v>
       </c>
       <c r="G285">
-        <v>0.26604899999999998</v>
+        <v>0.37960650000000001</v>
       </c>
       <c r="H285">
         <v>1265</v>
@@ -30250,7 +30250,7 @@
         <v>0.126</v>
       </c>
       <c r="G286">
-        <v>0.29560999999999998</v>
+        <v>0.42178499999999997</v>
       </c>
       <c r="H286">
         <v>1265</v>
@@ -30303,7 +30303,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
       <c r="G287">
-        <v>0.26604899999999998</v>
+        <v>0.37960650000000001</v>
       </c>
       <c r="H287">
         <v>1485.0000000000002</v>
@@ -30356,7 +30356,7 @@
         <v>2.2499999999999999E-2</v>
       </c>
       <c r="G288">
-        <v>0.261826</v>
+        <v>0.373581</v>
       </c>
       <c r="H288">
         <v>1930.5000000000002</v>
@@ -30409,7 +30409,7 @@
         <v>2.2499999999999999E-2</v>
       </c>
       <c r="G289">
-        <v>0.261826</v>
+        <v>0.373581</v>
       </c>
       <c r="H289">
         <v>1930.5000000000002</v>
@@ -30462,7 +30462,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
       <c r="G290">
-        <v>0.24493399999999996</v>
+        <v>0.34947899999999993</v>
       </c>
       <c r="H290">
         <v>1930.5000000000002</v>
@@ -30515,7 +30515,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
       <c r="G291">
-        <v>0.25337999999999999</v>
+        <v>0.36152999999999996</v>
       </c>
       <c r="H291">
         <v>1930.5000000000005</v>
@@ -30568,7 +30568,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
       <c r="G292">
-        <v>0.27449500000000004</v>
+        <v>0.3916575000000001</v>
       </c>
       <c r="H292">
         <v>1930.5000000000007</v>
@@ -30621,7 +30621,7 @@
         <v>2.4E-2</v>
       </c>
       <c r="G293">
-        <v>0.23648800000000003</v>
+        <v>0.33742800000000001</v>
       </c>
       <c r="H293">
         <v>1930.5000000000007</v>
@@ -30674,7 +30674,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
       <c r="G294">
-        <v>0.24493399999999999</v>
+        <v>0.34947899999999993</v>
       </c>
       <c r="H294">
         <v>1930.5000000000005</v>
@@ -30727,7 +30727,7 @@
         <v>2.3E-2</v>
       </c>
       <c r="G295">
-        <v>0.24493399999999996</v>
+        <v>0.34947899999999993</v>
       </c>
       <c r="H295">
         <v>1930.5000000000002</v>
@@ -30780,7 +30780,7 @@
         <v>2.4E-2</v>
       </c>
       <c r="G296">
-        <v>0.23648800000000003</v>
+        <v>0.33742800000000001</v>
       </c>
       <c r="H296">
         <v>1930.5000000000007</v>
@@ -30801,7 +30801,7 @@
         <v>315</v>
       </c>
       <c r="P296" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="Q296" t="s">
         <v>434</v>
@@ -30836,7 +30836,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L297">
-        <v>0.17165578681961033</v>
+        <v>0.17165578681961038</v>
       </c>
       <c r="N297" t="s">
         <v>432</v>
@@ -30845,7 +30845,7 @@
         <v>315</v>
       </c>
       <c r="P297" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q297" t="s">
         <v>434</v>
@@ -30880,7 +30880,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L298">
-        <v>0.17165578681961033</v>
+        <v>0.17165578681961038</v>
       </c>
       <c r="N298" t="s">
         <v>432</v>
@@ -30924,7 +30924,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L299">
-        <v>0.17165578681961033</v>
+        <v>0.17165578681961038</v>
       </c>
       <c r="N299" t="s">
         <v>432</v>
@@ -31325,7 +31325,7 @@
         <v>330</v>
       </c>
       <c r="P306" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q306" t="s">
         <v>434</v>
@@ -31381,7 +31381,7 @@
         <v>330</v>
       </c>
       <c r="P307" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="Q307" t="s">
         <v>434</v>
@@ -31717,7 +31717,7 @@
         <v>342</v>
       </c>
       <c r="P313" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q313" t="s">
         <v>434</v>
@@ -31773,7 +31773,7 @@
         <v>342</v>
       </c>
       <c r="P314" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="Q314" t="s">
         <v>434</v>
@@ -31829,7 +31829,7 @@
         <v>344</v>
       </c>
       <c r="P315" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q315" t="s">
         <v>434</v>
@@ -31885,7 +31885,7 @@
         <v>344</v>
       </c>
       <c r="P316" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="Q316" t="s">
         <v>434</v>
@@ -32165,7 +32165,7 @@
         <v>354</v>
       </c>
       <c r="P321" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="Q321" t="s">
         <v>434</v>
@@ -32221,7 +32221,7 @@
         <v>354</v>
       </c>
       <c r="P322" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q322" t="s">
         <v>434</v>
@@ -32333,7 +32333,7 @@
         <v>358</v>
       </c>
       <c r="P324" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="Q324" t="s">
         <v>434</v>
@@ -32389,7 +32389,7 @@
         <v>358</v>
       </c>
       <c r="P325" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q325" t="s">
         <v>434</v>
@@ -32445,7 +32445,7 @@
         <v>360</v>
       </c>
       <c r="P326" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="Q326" t="s">
         <v>434</v>
@@ -32501,7 +32501,7 @@
         <v>360</v>
       </c>
       <c r="P327" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q327" t="s">
         <v>434</v>
@@ -33005,7 +33005,7 @@
         <v>375</v>
       </c>
       <c r="P336" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q336" t="s">
         <v>434</v>
@@ -33061,7 +33061,7 @@
         <v>375</v>
       </c>
       <c r="P337" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="Q337" t="s">
         <v>434</v>
@@ -33565,7 +33565,7 @@
         <v>389</v>
       </c>
       <c r="P346" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="Q346" t="s">
         <v>434</v>
@@ -33621,7 +33621,7 @@
         <v>389</v>
       </c>
       <c r="P347" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q347" t="s">
         <v>434</v>
@@ -33957,7 +33957,7 @@
         <v>401</v>
       </c>
       <c r="P353" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="Q353" t="s">
         <v>434</v>
@@ -34013,7 +34013,7 @@
         <v>401</v>
       </c>
       <c r="P354" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q354" t="s">
         <v>434</v>
@@ -34069,7 +34069,7 @@
         <v>403</v>
       </c>
       <c r="P355" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q355" t="s">
         <v>434</v>
@@ -34125,7 +34125,7 @@
         <v>403</v>
       </c>
       <c r="P356" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="Q356" t="s">
         <v>434</v>
@@ -34181,7 +34181,7 @@
         <v>405</v>
       </c>
       <c r="P357" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="Q357" t="s">
         <v>434</v>
@@ -34237,7 +34237,7 @@
         <v>405</v>
       </c>
       <c r="P358" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q358" t="s">
         <v>434</v>
@@ -34405,7 +34405,7 @@
         <v>409</v>
       </c>
       <c r="P361" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="Q361" t="s">
         <v>434</v>
@@ -34461,7 +34461,7 @@
         <v>409</v>
       </c>
       <c r="P362" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q362" t="s">
         <v>434</v>
@@ -34573,7 +34573,7 @@
         <v>413</v>
       </c>
       <c r="P364" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="Q364" t="s">
         <v>434</v>
@@ -34629,7 +34629,7 @@
         <v>413</v>
       </c>
       <c r="P365" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q365" t="s">
         <v>434</v>
@@ -34741,7 +34741,7 @@
         <v>417</v>
       </c>
       <c r="P367" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q367" t="s">
         <v>434</v>
@@ -34797,7 +34797,7 @@
         <v>417</v>
       </c>
       <c r="P368" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="Q368" t="s">
         <v>434</v>
@@ -34853,7 +34853,7 @@
         <v>419</v>
       </c>
       <c r="P369" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q369" t="s">
         <v>434</v>
@@ -34909,7 +34909,7 @@
         <v>419</v>
       </c>
       <c r="P370" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="Q370" t="s">
         <v>434</v>
@@ -44086,7 +44086,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L631">
-        <v>0.48643306464952119</v>
+        <v>0.48643306464952113</v>
       </c>
     </row>
     <row r="632" spans="2:12" x14ac:dyDescent="0.45">
@@ -44109,7 +44109,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L632">
-        <v>0.48643306464952119</v>
+        <v>0.48643306464952113</v>
       </c>
     </row>
     <row r="633" spans="2:12" x14ac:dyDescent="0.45">
@@ -44132,7 +44132,7 @@
         <v>0.33122999999999997</v>
       </c>
       <c r="L633">
-        <v>0.48643306464952119</v>
+        <v>0.48643306464952113</v>
       </c>
     </row>
     <row r="634" spans="2:12" x14ac:dyDescent="0.45">
@@ -52611,7 +52611,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69E80768-FCEE-40B0-90DF-6FAA7F1747B8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06224567-2E60-4AA1-A4B7-550548A1A895}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_FRA_grids_syn_5/vt_vervestacks_FRA_v1.xlsx
+++ b/VerveStacks_FRA_grids_syn_5/vt_vervestacks_FRA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_syn_5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8FDB1C97-4E18-40BA-ACA7-68CFEDA7DB87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{76769DF1-70E2-478A-BC80-5A9F61D17EB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{0A2D2DBA-76B1-49A5-B29F-07440C9376AA}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="12682" xr2:uid="{C8406A90-2A5F-4873-85B3-49B77FBE106D}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -3598,7 +3598,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98133229-CCC6-4A9B-B51A-1552AAAD123F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFD16C67-10A6-4E4F-8F96-F7A5EAB5CF07}">
   <dimension ref="B9:T115"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3733,7 +3733,7 @@
         <v>19</v>
       </c>
       <c r="E12">
-        <v>0.12083270400000001</v>
+        <v>0.10069392000000002</v>
       </c>
       <c r="F12">
         <v>3583</v>
@@ -3789,7 +3789,7 @@
         <v>29</v>
       </c>
       <c r="E13">
-        <v>0.12083270400000001</v>
+        <v>0.10069392000000005</v>
       </c>
       <c r="F13">
         <v>3583</v>
@@ -3845,7 +3845,7 @@
         <v>19</v>
       </c>
       <c r="E14">
-        <v>0.33007380000000003</v>
+        <v>0.27506149999999996</v>
       </c>
       <c r="F14">
         <v>1967</v>
@@ -3901,7 +3901,7 @@
         <v>19</v>
       </c>
       <c r="E15">
-        <v>0.33007380000000003</v>
+        <v>0.27506149999999996</v>
       </c>
       <c r="F15">
         <v>1967</v>
@@ -3957,7 +3957,7 @@
         <v>29</v>
       </c>
       <c r="E16">
-        <v>0.33007379999999997</v>
+        <v>0.27506149999999996</v>
       </c>
       <c r="F16">
         <v>1967</v>
@@ -4013,7 +4013,7 @@
         <v>16</v>
       </c>
       <c r="E17">
-        <v>0.5483205000000001</v>
+        <v>0.46865000000000007</v>
       </c>
       <c r="F17">
         <v>1365</v>
@@ -4069,7 +4069,7 @@
         <v>16</v>
       </c>
       <c r="E18">
-        <v>0.5483205000000001</v>
+        <v>0.46865000000000007</v>
       </c>
       <c r="F18">
         <v>1365</v>
@@ -4125,7 +4125,7 @@
         <v>21</v>
       </c>
       <c r="E19">
-        <v>0.61158824999999983</v>
+        <v>0.52272499999999988</v>
       </c>
       <c r="F19">
         <v>1365</v>
@@ -4181,7 +4181,7 @@
         <v>29</v>
       </c>
       <c r="E20">
-        <v>0.61158824999999983</v>
+        <v>0.52272499999999988</v>
       </c>
       <c r="F20">
         <v>1365</v>
@@ -4237,7 +4237,7 @@
         <v>16</v>
       </c>
       <c r="E21">
-        <v>0.61158824999999983</v>
+        <v>0.52272499999999988</v>
       </c>
       <c r="F21">
         <v>1365</v>
@@ -4293,7 +4293,7 @@
         <v>21</v>
       </c>
       <c r="E22">
-        <v>0.57468206249999987</v>
+        <v>0.49118125000000001</v>
       </c>
       <c r="F22">
         <v>1365</v>
@@ -4349,7 +4349,7 @@
         <v>29</v>
       </c>
       <c r="E23">
-        <v>0.61158824999999983</v>
+        <v>0.52272499999999988</v>
       </c>
       <c r="F23">
         <v>1365</v>
@@ -4405,7 +4405,7 @@
         <v>21</v>
       </c>
       <c r="E24">
-        <v>0.57468206250000009</v>
+        <v>0.49118125000000001</v>
       </c>
       <c r="F24">
         <v>1365</v>
@@ -4461,7 +4461,7 @@
         <v>16</v>
       </c>
       <c r="E25">
-        <v>0.57468206249999998</v>
+        <v>0.49118125000000001</v>
       </c>
       <c r="F25">
         <v>1365</v>
@@ -4517,7 +4517,7 @@
         <v>16</v>
       </c>
       <c r="E26">
-        <v>0.57468206249999998</v>
+        <v>0.49118125000000001</v>
       </c>
       <c r="F26">
         <v>1365</v>
@@ -4573,7 +4573,7 @@
         <v>29</v>
       </c>
       <c r="E27">
-        <v>0.57468206249999998</v>
+        <v>0.49118125000000001</v>
       </c>
       <c r="F27">
         <v>1365</v>
@@ -4629,7 +4629,7 @@
         <v>29</v>
       </c>
       <c r="E28">
-        <v>0.57468206249999998</v>
+        <v>0.49118125000000001</v>
       </c>
       <c r="F28">
         <v>1365</v>
@@ -4685,7 +4685,7 @@
         <v>21</v>
       </c>
       <c r="E29">
-        <v>0.61158824999999983</v>
+        <v>0.52272499999999988</v>
       </c>
       <c r="F29">
         <v>1365</v>
@@ -4741,7 +4741,7 @@
         <v>21</v>
       </c>
       <c r="E30">
-        <v>0.61158824999999983</v>
+        <v>0.52272499999999988</v>
       </c>
       <c r="F30">
         <v>1365</v>
@@ -4797,7 +4797,7 @@
         <v>19</v>
       </c>
       <c r="E31">
-        <v>0.57468206249999998</v>
+        <v>0.49118125000000001</v>
       </c>
       <c r="F31">
         <v>1365</v>
@@ -4853,7 +4853,7 @@
         <v>16</v>
       </c>
       <c r="E32">
-        <v>0.57468206249999998</v>
+        <v>0.49118125000000001</v>
       </c>
       <c r="F32">
         <v>1365</v>
@@ -4909,7 +4909,7 @@
         <v>16</v>
       </c>
       <c r="E33">
-        <v>0.52723125000000004</v>
+        <v>0.450625</v>
       </c>
       <c r="F33">
         <v>1365</v>
@@ -4965,7 +4965,7 @@
         <v>19</v>
       </c>
       <c r="E34">
-        <v>0.63267750000000011</v>
+        <v>0.54075000000000006</v>
       </c>
       <c r="F34">
         <v>1365</v>
@@ -5021,7 +5021,7 @@
         <v>16</v>
       </c>
       <c r="E35">
-        <v>0.27943256250000004</v>
+        <v>0.23883125000000002</v>
       </c>
       <c r="F35">
         <v>1365</v>
@@ -5077,7 +5077,7 @@
         <v>16</v>
       </c>
       <c r="E36">
-        <v>0.30579412499999992</v>
+        <v>0.26136249999999994</v>
       </c>
       <c r="F36">
         <v>1365</v>
@@ -5133,7 +5133,7 @@
         <v>16</v>
       </c>
       <c r="E37">
-        <v>0.30579412499999992</v>
+        <v>0.26136249999999994</v>
       </c>
       <c r="F37">
         <v>1365</v>
@@ -5189,7 +5189,7 @@
         <v>16</v>
       </c>
       <c r="E38">
-        <v>0.30579412499999992</v>
+        <v>0.26136249999999994</v>
       </c>
       <c r="F38">
         <v>1365</v>
@@ -5245,7 +5245,7 @@
         <v>21</v>
       </c>
       <c r="E39">
-        <v>0.2952495</v>
+        <v>0.25235000000000002</v>
       </c>
       <c r="F39">
         <v>1365</v>
@@ -5301,7 +5301,7 @@
         <v>21</v>
       </c>
       <c r="E40">
-        <v>0.23198174999999996</v>
+        <v>0.19827499999999998</v>
       </c>
       <c r="F40">
         <v>1365</v>
@@ -5357,7 +5357,7 @@
         <v>21</v>
       </c>
       <c r="E41">
-        <v>0.23198174999999996</v>
+        <v>0.19827499999999998</v>
       </c>
       <c r="F41">
         <v>1365</v>
@@ -5413,7 +5413,7 @@
         <v>21</v>
       </c>
       <c r="E42">
-        <v>0.21089250000000001</v>
+        <v>0.18025000000000002</v>
       </c>
       <c r="F42">
         <v>1365</v>
@@ -5469,7 +5469,7 @@
         <v>29</v>
       </c>
       <c r="E43">
-        <v>0.2952495</v>
+        <v>0.25235000000000002</v>
       </c>
       <c r="F43">
         <v>1365</v>
@@ -5525,7 +5525,7 @@
         <v>16</v>
       </c>
       <c r="E44">
-        <v>0.30579412499999992</v>
+        <v>0.26136249999999994</v>
       </c>
       <c r="F44">
         <v>1365</v>
@@ -5581,7 +5581,7 @@
         <v>16</v>
       </c>
       <c r="E45">
-        <v>0.2952495</v>
+        <v>0.25235000000000002</v>
       </c>
       <c r="F45">
         <v>1365</v>
@@ -5637,7 +5637,7 @@
         <v>29</v>
       </c>
       <c r="E46">
-        <v>0.26888793749999995</v>
+        <v>0.22981874999999999</v>
       </c>
       <c r="F46">
         <v>1365</v>
@@ -5693,7 +5693,7 @@
         <v>19</v>
       </c>
       <c r="E47">
-        <v>0.26888793749999995</v>
+        <v>0.22981874999999999</v>
       </c>
       <c r="F47">
         <v>1365</v>
@@ -5749,7 +5749,7 @@
         <v>16</v>
       </c>
       <c r="E48">
-        <v>0.26888793749999995</v>
+        <v>0.22981874999999999</v>
       </c>
       <c r="F48">
         <v>1365</v>
@@ -5805,7 +5805,7 @@
         <v>16</v>
       </c>
       <c r="E49">
-        <v>0.2952495</v>
+        <v>0.25235000000000002</v>
       </c>
       <c r="F49">
         <v>1365</v>
@@ -5861,7 +5861,7 @@
         <v>21</v>
       </c>
       <c r="E50">
-        <v>0.26888793749999995</v>
+        <v>0.22981874999999999</v>
       </c>
       <c r="F50">
         <v>1365</v>
@@ -5917,7 +5917,7 @@
         <v>16</v>
       </c>
       <c r="E51">
-        <v>0.26888793749999995</v>
+        <v>0.22981874999999999</v>
       </c>
       <c r="F51">
         <v>1365</v>
@@ -5973,7 +5973,7 @@
         <v>21</v>
       </c>
       <c r="E52">
-        <v>0.26888793749999995</v>
+        <v>0.22981874999999999</v>
       </c>
       <c r="F52">
         <v>1365</v>
@@ -6029,7 +6029,7 @@
         <v>16</v>
       </c>
       <c r="E53">
-        <v>0.2952495</v>
+        <v>0.25235000000000002</v>
       </c>
       <c r="F53">
         <v>1365</v>
@@ -6085,7 +6085,7 @@
         <v>16</v>
       </c>
       <c r="E54">
-        <v>0.31633874999999995</v>
+        <v>0.27037500000000003</v>
       </c>
       <c r="F54">
         <v>1365</v>
@@ -6141,7 +6141,7 @@
         <v>16</v>
       </c>
       <c r="E55">
-        <v>0.31633874999999995</v>
+        <v>0.27037500000000003</v>
       </c>
       <c r="F55">
         <v>1365</v>
@@ -6197,7 +6197,7 @@
         <v>29</v>
       </c>
       <c r="E56">
-        <v>0.31633874999999995</v>
+        <v>0.27037500000000003</v>
       </c>
       <c r="F56">
         <v>1365</v>
@@ -6253,7 +6253,7 @@
         <v>29</v>
       </c>
       <c r="E57">
-        <v>0.31633874999999995</v>
+        <v>0.27037500000000003</v>
       </c>
       <c r="F57">
         <v>1365</v>
@@ -6309,7 +6309,7 @@
         <v>29</v>
       </c>
       <c r="E58">
-        <v>0.2952495</v>
+        <v>0.25235000000000002</v>
       </c>
       <c r="F58">
         <v>1365</v>
@@ -6365,7 +6365,7 @@
         <v>21</v>
       </c>
       <c r="E59">
-        <v>0.31633874999999995</v>
+        <v>0.27037500000000003</v>
       </c>
       <c r="F59">
         <v>1365</v>
@@ -6421,7 +6421,7 @@
         <v>21</v>
       </c>
       <c r="E60">
-        <v>0.26888793749999995</v>
+        <v>0.22981874999999999</v>
       </c>
       <c r="F60">
         <v>1365</v>
@@ -6477,7 +6477,7 @@
         <v>21</v>
       </c>
       <c r="E61">
-        <v>0.26888793749999995</v>
+        <v>0.22981874999999999</v>
       </c>
       <c r="F61">
         <v>1365</v>
@@ -6533,7 +6533,7 @@
         <v>16</v>
       </c>
       <c r="E62">
-        <v>0.23198174999999996</v>
+        <v>0.19827500000000001</v>
       </c>
       <c r="F62">
         <v>1365</v>
@@ -6589,7 +6589,7 @@
         <v>19</v>
       </c>
       <c r="E63">
-        <v>0.33909671250000012</v>
+        <v>0.28982625000000001</v>
       </c>
       <c r="F63">
         <v>1365</v>
@@ -6645,7 +6645,7 @@
         <v>21</v>
       </c>
       <c r="E64">
-        <v>0.33909671250000001</v>
+        <v>0.28982625000000001</v>
       </c>
       <c r="F64">
         <v>1365</v>
@@ -6701,7 +6701,7 @@
         <v>16</v>
       </c>
       <c r="E65">
-        <v>0.33909671250000001</v>
+        <v>0.28982625000000001</v>
       </c>
       <c r="F65">
         <v>1365</v>
@@ -6757,7 +6757,7 @@
         <v>29</v>
       </c>
       <c r="E66">
-        <v>0.33909671250000001</v>
+        <v>0.28982625000000001</v>
       </c>
       <c r="F66">
         <v>1365</v>
@@ -6813,7 +6813,7 @@
         <v>85</v>
       </c>
       <c r="E67">
-        <v>0.33909671250000001</v>
+        <v>0.28982625000000001</v>
       </c>
       <c r="F67">
         <v>1365</v>
@@ -6869,7 +6869,7 @@
         <v>29</v>
       </c>
       <c r="E68">
-        <v>0.37433418749999992</v>
+        <v>0.31994374999999997</v>
       </c>
       <c r="F68">
         <v>1365</v>
@@ -6925,7 +6925,7 @@
         <v>29</v>
       </c>
       <c r="E69">
-        <v>0.37433418749999992</v>
+        <v>0.31994374999999997</v>
       </c>
       <c r="F69">
         <v>1365</v>
@@ -6981,7 +6981,7 @@
         <v>85</v>
       </c>
       <c r="E70">
-        <v>0.34797262500000004</v>
+        <v>0.29741250000000002</v>
       </c>
       <c r="F70">
         <v>1365</v>
@@ -7037,7 +7037,7 @@
         <v>85</v>
       </c>
       <c r="E71">
-        <v>0.34797262499999992</v>
+        <v>0.29741250000000002</v>
       </c>
       <c r="F71">
         <v>1365</v>
@@ -7093,7 +7093,7 @@
         <v>85</v>
       </c>
       <c r="E72">
-        <v>0.34797262499999992</v>
+        <v>0.29741250000000002</v>
       </c>
       <c r="F72">
         <v>1365</v>
@@ -7149,7 +7149,7 @@
         <v>21</v>
       </c>
       <c r="E73">
-        <v>0.31633874999999995</v>
+        <v>0.27037500000000003</v>
       </c>
       <c r="F73">
         <v>1365</v>
@@ -7205,7 +7205,7 @@
         <v>21</v>
       </c>
       <c r="E74">
-        <v>0.31633874999999995</v>
+        <v>0.27037500000000003</v>
       </c>
       <c r="F74">
         <v>1365</v>
@@ -7261,7 +7261,7 @@
         <v>21</v>
       </c>
       <c r="E75">
-        <v>0.35324493750000002</v>
+        <v>0.30191875000000001</v>
       </c>
       <c r="F75">
         <v>1365</v>
@@ -7317,7 +7317,7 @@
         <v>21</v>
       </c>
       <c r="E76">
-        <v>0.35324493750000002</v>
+        <v>0.30191875000000001</v>
       </c>
       <c r="F76">
         <v>1365</v>
@@ -7373,7 +7373,7 @@
         <v>21</v>
       </c>
       <c r="E77">
-        <v>0.34797262500000004</v>
+        <v>0.29741250000000002</v>
       </c>
       <c r="F77">
         <v>1365</v>
@@ -7429,7 +7429,7 @@
         <v>21</v>
       </c>
       <c r="E78">
-        <v>0.33742799999999995</v>
+        <v>0.28839999999999999</v>
       </c>
       <c r="F78">
         <v>1365</v>
@@ -7485,7 +7485,7 @@
         <v>16</v>
       </c>
       <c r="E79">
-        <v>0.35324493750000002</v>
+        <v>0.30191875000000001</v>
       </c>
       <c r="F79">
         <v>1365</v>
@@ -7541,7 +7541,7 @@
         <v>16</v>
       </c>
       <c r="E80">
-        <v>0.35324493750000002</v>
+        <v>0.30191875000000001</v>
       </c>
       <c r="F80">
         <v>1365</v>
@@ -7597,7 +7597,7 @@
         <v>85</v>
       </c>
       <c r="E81">
-        <v>0.33742799999999995</v>
+        <v>0.28839999999999999</v>
       </c>
       <c r="F81">
         <v>1365</v>
@@ -7653,7 +7653,7 @@
         <v>16</v>
       </c>
       <c r="E82">
-        <v>0.34797262500000004</v>
+        <v>0.29741250000000002</v>
       </c>
       <c r="F82">
         <v>1365</v>
@@ -7709,7 +7709,7 @@
         <v>21</v>
       </c>
       <c r="E83">
-        <v>0.50614199999999998</v>
+        <v>0.43259999999999998</v>
       </c>
       <c r="F83">
         <v>1365</v>
@@ -7765,7 +7765,7 @@
         <v>16</v>
       </c>
       <c r="E84">
-        <v>0.52723125000000004</v>
+        <v>0.450625</v>
       </c>
       <c r="F84">
         <v>1365</v>
@@ -7821,7 +7821,7 @@
         <v>16</v>
       </c>
       <c r="E85">
-        <v>0.52723125000000004</v>
+        <v>0.450625</v>
       </c>
       <c r="F85">
         <v>1365</v>
@@ -7877,7 +7877,7 @@
         <v>16</v>
       </c>
       <c r="E86">
-        <v>0.52723125000000004</v>
+        <v>0.450625</v>
       </c>
       <c r="F86">
         <v>1365</v>
@@ -7933,7 +7933,7 @@
         <v>85</v>
       </c>
       <c r="E87">
-        <v>0.52723125000000004</v>
+        <v>0.450625</v>
       </c>
       <c r="F87">
         <v>1365</v>
@@ -7989,7 +7989,7 @@
         <v>16</v>
       </c>
       <c r="E88">
-        <v>0.2952495</v>
+        <v>0.25235000000000002</v>
       </c>
       <c r="F88">
         <v>1365</v>
@@ -8045,7 +8045,7 @@
         <v>16</v>
       </c>
       <c r="E89">
-        <v>0.26888793749999995</v>
+        <v>0.22981874999999999</v>
       </c>
       <c r="F89">
         <v>1365</v>
@@ -8101,7 +8101,7 @@
         <v>19</v>
       </c>
       <c r="E90">
-        <v>0.30579412499999992</v>
+        <v>0.26136249999999994</v>
       </c>
       <c r="F90">
         <v>1365</v>
@@ -8157,7 +8157,7 @@
         <v>21</v>
       </c>
       <c r="E91">
-        <v>0.28470487499999997</v>
+        <v>0.24333750000000001</v>
       </c>
       <c r="F91">
         <v>1365</v>
@@ -8213,7 +8213,7 @@
         <v>29</v>
       </c>
       <c r="E92">
-        <v>0.30579412499999992</v>
+        <v>0.26136249999999994</v>
       </c>
       <c r="F92">
         <v>1365</v>
@@ -8269,7 +8269,7 @@
         <v>21</v>
       </c>
       <c r="E93">
-        <v>0.28470487499999997</v>
+        <v>0.24333750000000001</v>
       </c>
       <c r="F93">
         <v>1365</v>
@@ -8325,7 +8325,7 @@
         <v>21</v>
       </c>
       <c r="E94">
-        <v>0.25834331249999998</v>
+        <v>0.22080625000000001</v>
       </c>
       <c r="F94">
         <v>1365</v>
@@ -8381,7 +8381,7 @@
         <v>21</v>
       </c>
       <c r="E95">
-        <v>0.25834331249999998</v>
+        <v>0.22080625000000001</v>
       </c>
       <c r="F95">
         <v>1365</v>
@@ -8437,7 +8437,7 @@
         <v>21</v>
       </c>
       <c r="E96">
-        <v>0.25834331249999998</v>
+        <v>0.22080625000000001</v>
       </c>
       <c r="F96">
         <v>1365</v>
@@ -8493,7 +8493,7 @@
         <v>29</v>
       </c>
       <c r="E97">
-        <v>0.25307099999999999</v>
+        <v>0.21629999999999999</v>
       </c>
       <c r="F97">
         <v>1365</v>
@@ -8549,7 +8549,7 @@
         <v>29</v>
       </c>
       <c r="E98">
-        <v>0.23198174999999996</v>
+        <v>0.19827500000000001</v>
       </c>
       <c r="F98">
         <v>1365</v>
@@ -8605,7 +8605,7 @@
         <v>19</v>
       </c>
       <c r="E99">
-        <v>0.25307099999999999</v>
+        <v>0.21629999999999999</v>
       </c>
       <c r="F99">
         <v>1365</v>
@@ -8661,7 +8661,7 @@
         <v>19</v>
       </c>
       <c r="E100">
-        <v>0.26888793749999995</v>
+        <v>0.22981874999999999</v>
       </c>
       <c r="F100">
         <v>1365</v>
@@ -8717,7 +8717,7 @@
         <v>19</v>
       </c>
       <c r="E101">
-        <v>0.23198174999999996</v>
+        <v>0.19827500000000001</v>
       </c>
       <c r="F101">
         <v>1365</v>
@@ -8773,7 +8773,7 @@
         <v>14</v>
       </c>
       <c r="E102">
-        <v>0.28470487499999997</v>
+        <v>0.24333750000000001</v>
       </c>
       <c r="F102">
         <v>1365</v>
@@ -8829,7 +8829,7 @@
         <v>14</v>
       </c>
       <c r="E103">
-        <v>0.28470487499999997</v>
+        <v>0.24333750000000001</v>
       </c>
       <c r="F103">
         <v>1365</v>
@@ -8885,7 +8885,7 @@
         <v>21</v>
       </c>
       <c r="E104">
-        <v>0.33215568750000002</v>
+        <v>0.28389375</v>
       </c>
       <c r="F104">
         <v>1365</v>
@@ -8941,7 +8941,7 @@
         <v>21</v>
       </c>
       <c r="E105">
-        <v>0.36906187499999993</v>
+        <v>0.31543749999999998</v>
       </c>
       <c r="F105">
         <v>1365</v>
@@ -8997,7 +8997,7 @@
         <v>19</v>
       </c>
       <c r="E106">
-        <v>0.33215568750000002</v>
+        <v>0.28389375</v>
       </c>
       <c r="F106">
         <v>1365</v>
@@ -9053,7 +9053,7 @@
         <v>29</v>
       </c>
       <c r="E107">
-        <v>0.32688337500000003</v>
+        <v>0.27938750000000001</v>
       </c>
       <c r="F107">
         <v>1365</v>
@@ -9109,7 +9109,7 @@
         <v>29</v>
       </c>
       <c r="E108">
-        <v>0.32688337500000003</v>
+        <v>0.27938750000000001</v>
       </c>
       <c r="F108">
         <v>1365</v>
@@ -9165,7 +9165,7 @@
         <v>21</v>
       </c>
       <c r="E109">
-        <v>0.30579412499999992</v>
+        <v>0.26136249999999994</v>
       </c>
       <c r="F109">
         <v>1365</v>
@@ -9221,7 +9221,7 @@
         <v>21</v>
       </c>
       <c r="E110">
-        <v>0.31633874999999995</v>
+        <v>0.27037500000000003</v>
       </c>
       <c r="F110">
         <v>1365</v>
@@ -9277,7 +9277,7 @@
         <v>21</v>
       </c>
       <c r="E111">
-        <v>0.3427003125000001</v>
+        <v>0.29290625000000003</v>
       </c>
       <c r="F111">
         <v>1365</v>
@@ -9333,7 +9333,7 @@
         <v>16</v>
       </c>
       <c r="E112">
-        <v>0.2952495</v>
+        <v>0.25235000000000002</v>
       </c>
       <c r="F112">
         <v>1365</v>
@@ -9389,7 +9389,7 @@
         <v>16</v>
       </c>
       <c r="E113">
-        <v>0.30579412499999992</v>
+        <v>0.26136249999999994</v>
       </c>
       <c r="F113">
         <v>1365</v>
@@ -9445,7 +9445,7 @@
         <v>16</v>
       </c>
       <c r="E114">
-        <v>0.30579412499999992</v>
+        <v>0.26136249999999994</v>
       </c>
       <c r="F114">
         <v>1365</v>
@@ -9501,7 +9501,7 @@
         <v>16</v>
       </c>
       <c r="E115">
-        <v>0.2952495</v>
+        <v>0.25235000000000002</v>
       </c>
       <c r="F115">
         <v>1365</v>
@@ -9552,7 +9552,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B9421C6-9EEB-4D79-A536-0AA4D1C4F68B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C56E958A-DBCB-4E90-A8E7-EDB5D03ED2B7}">
   <dimension ref="B9:T130"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15728,7 +15728,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{968AA02A-CE15-4383-BC39-F94673774035}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F701D514-F4B3-46AF-A063-4947F91E842E}">
   <dimension ref="B9:T875"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15813,7 +15813,7 @@
         <v>0.06</v>
       </c>
       <c r="G11">
-        <v>0.39551999999999998</v>
+        <v>0.3296</v>
       </c>
       <c r="H11">
         <v>5197.5</v>
@@ -15866,7 +15866,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
       <c r="G12">
-        <v>0.39551999999999998</v>
+        <v>0.3296</v>
       </c>
       <c r="H12">
         <v>5197.5</v>
@@ -15919,7 +15919,7 @@
         <v>5.1999999999999998E-2</v>
       </c>
       <c r="G13">
-        <v>0.35843999999999993</v>
+        <v>0.29869999999999997</v>
       </c>
       <c r="H13">
         <v>4427.5</v>
@@ -15972,7 +15972,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
       <c r="G14">
-        <v>0.28428000000000003</v>
+        <v>0.23690000000000003</v>
       </c>
       <c r="H14">
         <v>4427.5</v>
@@ -16025,7 +16025,7 @@
         <v>0.05</v>
       </c>
       <c r="G15">
-        <v>0.34608000000000005</v>
+        <v>0.28840000000000005</v>
       </c>
       <c r="H15">
         <v>5197.5</v>
@@ -16078,7 +16078,7 @@
         <v>0.15</v>
       </c>
       <c r="G16">
-        <v>0.32754</v>
+        <v>0.27295000000000003</v>
       </c>
       <c r="H16">
         <v>4427.5</v>
@@ -16131,7 +16131,7 @@
         <v>0.20313807531380754</v>
       </c>
       <c r="G17">
-        <v>0.40788000000000008</v>
+        <v>0.33990000000000004</v>
       </c>
       <c r="H17">
         <v>4427.5</v>
@@ -16184,7 +16184,7 @@
         <v>1.1375732217573222</v>
       </c>
       <c r="G18">
-        <v>0.43259999999999998</v>
+        <v>0.36049999999999999</v>
       </c>
       <c r="H18">
         <v>3850.0000000000009</v>
@@ -16237,7 +16237,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
       <c r="G19">
-        <v>0.31517999999999996</v>
+        <v>0.26264999999999999</v>
       </c>
       <c r="H19">
         <v>5197.5</v>
@@ -16290,7 +16290,7 @@
         <v>0.60128870292887027</v>
       </c>
       <c r="G20">
-        <v>0.43260000000000004</v>
+        <v>0.36049999999999999</v>
       </c>
       <c r="H20">
         <v>3850</v>
@@ -16343,7 +16343,7 @@
         <v>0.39841636077608789</v>
       </c>
       <c r="G21">
-        <v>0.397476</v>
+        <v>0.33123000000000002</v>
       </c>
       <c r="N21" t="s">
         <v>432</v>
@@ -16384,7 +16384,7 @@
         <v>0.20458363922391182</v>
       </c>
       <c r="G22">
-        <v>0.397476</v>
+        <v>0.33123000000000008</v>
       </c>
       <c r="N22" t="s">
         <v>432</v>
@@ -16425,7 +16425,7 @@
         <v>0.63</v>
       </c>
       <c r="G23">
-        <v>0.43260000000000004</v>
+        <v>0.36049999999999999</v>
       </c>
       <c r="H23">
         <v>2200</v>
@@ -16478,7 +16478,7 @@
         <v>0.63</v>
       </c>
       <c r="G24">
-        <v>0.43260000000000004</v>
+        <v>0.36049999999999999</v>
       </c>
       <c r="H24">
         <v>2200</v>
@@ -16531,7 +16531,7 @@
         <v>0.64700000000000002</v>
       </c>
       <c r="G25">
-        <v>0.43259999999999998</v>
+        <v>0.36049999999999999</v>
       </c>
       <c r="H25">
         <v>2200</v>
@@ -16584,7 +16584,7 @@
         <v>0.12</v>
       </c>
       <c r="G26">
-        <v>0.6266520000000001</v>
+        <v>0.53560000000000008</v>
       </c>
       <c r="H26">
         <v>1265</v>
@@ -16637,7 +16637,7 @@
         <v>0.12</v>
       </c>
       <c r="G27">
-        <v>0.6266520000000001</v>
+        <v>0.53560000000000008</v>
       </c>
       <c r="H27">
         <v>1265</v>
@@ -16690,7 +16690,7 @@
         <v>0.40100000000000002</v>
       </c>
       <c r="G28">
-        <v>0.69895799999999986</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H28">
         <v>1100</v>
@@ -16743,7 +16743,7 @@
         <v>0.42699999999999999</v>
       </c>
       <c r="G29">
-        <v>0.69895799999999986</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H29">
         <v>1100</v>
@@ -16796,7 +16796,7 @@
         <v>0.58499999999999996</v>
       </c>
       <c r="G30">
-        <v>0.69895799999999986</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H30">
         <v>1100</v>
@@ -16849,7 +16849,7 @@
         <v>0.45300000000000001</v>
       </c>
       <c r="G31">
-        <v>0.65677949999999985</v>
+        <v>0.56135000000000002</v>
       </c>
       <c r="H31">
         <v>1100</v>
@@ -16902,7 +16902,7 @@
         <v>0.41299999999999998</v>
       </c>
       <c r="G32">
-        <v>0.69895799999999986</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H32">
         <v>1100</v>
@@ -16955,7 +16955,7 @@
         <v>0.42799999999999999</v>
       </c>
       <c r="G33">
-        <v>0.65677950000000007</v>
+        <v>0.56135000000000002</v>
       </c>
       <c r="H33">
         <v>1100</v>
@@ -17008,7 +17008,7 @@
         <v>0.40400000000000003</v>
       </c>
       <c r="G34">
-        <v>0.65677949999999996</v>
+        <v>0.56135000000000002</v>
       </c>
       <c r="H34">
         <v>1100</v>
@@ -17061,7 +17061,7 @@
         <v>0.40400000000000003</v>
       </c>
       <c r="G35">
-        <v>0.65677949999999996</v>
+        <v>0.56135000000000002</v>
       </c>
       <c r="H35">
         <v>1100</v>
@@ -17114,7 +17114,7 @@
         <v>0.44</v>
       </c>
       <c r="G36">
-        <v>0.65677949999999996</v>
+        <v>0.56135000000000002</v>
       </c>
       <c r="H36">
         <v>1100</v>
@@ -17167,7 +17167,7 @@
         <v>0.44</v>
       </c>
       <c r="G37">
-        <v>0.65677949999999996</v>
+        <v>0.56135000000000002</v>
       </c>
       <c r="H37">
         <v>1100</v>
@@ -17220,7 +17220,7 @@
         <v>0.499</v>
       </c>
       <c r="G38">
-        <v>0.69895799999999986</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H38">
         <v>1100</v>
@@ -17273,7 +17273,7 @@
         <v>0.499</v>
       </c>
       <c r="G39">
-        <v>0.69895799999999986</v>
+        <v>0.59739999999999993</v>
       </c>
       <c r="H39">
         <v>1100</v>
@@ -17326,7 +17326,7 @@
         <v>0.435</v>
       </c>
       <c r="G40">
-        <v>0.65677949999999996</v>
+        <v>0.56135000000000002</v>
       </c>
       <c r="H40">
         <v>1100</v>
@@ -17379,7 +17379,7 @@
         <v>0.45</v>
       </c>
       <c r="G41">
-        <v>0.65677949999999996</v>
+        <v>0.56135000000000002</v>
       </c>
       <c r="H41">
         <v>1100</v>
@@ -17432,7 +17432,7 @@
         <v>0.13200000000000001</v>
       </c>
       <c r="G42">
-        <v>0.60255000000000003</v>
+        <v>0.51500000000000001</v>
       </c>
       <c r="H42">
         <v>1265</v>
@@ -17485,7 +17485,7 @@
         <v>0.44600000000000001</v>
       </c>
       <c r="G43">
-        <v>0.72306000000000004</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="H43">
         <v>1100</v>
@@ -17538,7 +17538,7 @@
         <v>0.20300000000000001</v>
       </c>
       <c r="G44">
-        <v>0.31935150000000001</v>
+        <v>0.27295000000000003</v>
       </c>
       <c r="H44">
         <v>1012</v>
@@ -17591,7 +17591,7 @@
         <v>0.125</v>
       </c>
       <c r="G45">
-        <v>0.34947899999999993</v>
+        <v>0.29869999999999997</v>
       </c>
       <c r="H45">
         <v>1012</v>
@@ -17644,7 +17644,7 @@
         <v>0.2</v>
       </c>
       <c r="G46">
-        <v>0.34947899999999987</v>
+        <v>0.29869999999999997</v>
       </c>
       <c r="H46">
         <v>1012</v>
@@ -17697,7 +17697,7 @@
         <v>0.2</v>
       </c>
       <c r="G47">
-        <v>0.34947899999999987</v>
+        <v>0.29869999999999997</v>
       </c>
       <c r="H47">
         <v>1012</v>
@@ -17750,7 +17750,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="G48">
-        <v>0.33742800000000001</v>
+        <v>0.28840000000000005</v>
       </c>
       <c r="H48">
         <v>1188</v>
@@ -17803,7 +17803,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
       <c r="G49">
-        <v>0.26512199999999997</v>
+        <v>0.22659999999999997</v>
       </c>
       <c r="H49">
         <v>1188</v>
@@ -17856,7 +17856,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
       <c r="G50">
-        <v>0.26512199999999997</v>
+        <v>0.22659999999999997</v>
       </c>
       <c r="H50">
         <v>1188</v>
@@ -17909,7 +17909,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
       <c r="G51">
-        <v>0.24101999999999998</v>
+        <v>0.20600000000000002</v>
       </c>
       <c r="H51">
         <v>1188</v>
@@ -17962,7 +17962,7 @@
         <v>0.02</v>
       </c>
       <c r="G52">
-        <v>0.33742800000000001</v>
+        <v>0.28840000000000005</v>
       </c>
       <c r="H52">
         <v>1188</v>
@@ -18015,7 +18015,7 @@
         <v>0.128</v>
       </c>
       <c r="G53">
-        <v>0.34947899999999993</v>
+        <v>0.29869999999999997</v>
       </c>
       <c r="H53">
         <v>1012</v>
@@ -18068,7 +18068,7 @@
         <v>4.7E-2</v>
       </c>
       <c r="G54">
-        <v>0.33742800000000001</v>
+        <v>0.28840000000000005</v>
       </c>
       <c r="H54">
         <v>1188</v>
@@ -18121,7 +18121,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="G55">
-        <v>0.30730049999999998</v>
+        <v>0.26264999999999999</v>
       </c>
       <c r="H55">
         <v>1188</v>
@@ -18174,7 +18174,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
       <c r="G56">
-        <v>0.30730049999999998</v>
+        <v>0.26264999999999999</v>
       </c>
       <c r="H56">
         <v>1188</v>
@@ -18227,7 +18227,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
       <c r="G57">
-        <v>0.30730049999999998</v>
+        <v>0.26264999999999999</v>
       </c>
       <c r="H57">
         <v>1188</v>
@@ -18280,7 +18280,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
       <c r="G58">
-        <v>0.33742800000000001</v>
+        <v>0.28840000000000005</v>
       </c>
       <c r="H58">
         <v>1188</v>
@@ -18333,7 +18333,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
       <c r="G59">
-        <v>0.30730049999999998</v>
+        <v>0.26264999999999999</v>
       </c>
       <c r="H59">
         <v>1188</v>
@@ -18386,7 +18386,7 @@
         <v>0.03</v>
       </c>
       <c r="G60">
-        <v>0.30730049999999998</v>
+        <v>0.26264999999999999</v>
       </c>
       <c r="H60">
         <v>1188</v>
@@ -18439,7 +18439,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="G61">
-        <v>0.30730049999999998</v>
+        <v>0.26264999999999999</v>
       </c>
       <c r="H61">
         <v>1188</v>
@@ -18492,7 +18492,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
       <c r="G62">
-        <v>0.33742800000000001</v>
+        <v>0.28840000000000005</v>
       </c>
       <c r="H62">
         <v>1188</v>
@@ -18545,7 +18545,7 @@
         <v>0.04</v>
       </c>
       <c r="G63">
-        <v>0.36152999999999996</v>
+        <v>0.309</v>
       </c>
       <c r="H63">
         <v>1188</v>
@@ -18598,7 +18598,7 @@
         <v>0.04</v>
       </c>
       <c r="G64">
-        <v>0.36152999999999996</v>
+        <v>0.309</v>
       </c>
       <c r="H64">
         <v>1188</v>
@@ -18651,7 +18651,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="G65">
-        <v>0.36152999999999996</v>
+        <v>0.309</v>
       </c>
       <c r="H65">
         <v>1188</v>
@@ -18704,7 +18704,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="G66">
-        <v>0.36152999999999996</v>
+        <v>0.309</v>
       </c>
       <c r="H66">
         <v>1188</v>
@@ -18757,7 +18757,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
       <c r="G67">
-        <v>0.33742800000000001</v>
+        <v>0.28840000000000005</v>
       </c>
       <c r="H67">
         <v>1188</v>
@@ -18810,7 +18810,7 @@
         <v>2.4500000000000001E-2</v>
       </c>
       <c r="G68">
-        <v>0.36152999999999996</v>
+        <v>0.309</v>
       </c>
       <c r="H68">
         <v>1188</v>
@@ -18863,7 +18863,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="G69">
-        <v>0.30730049999999998</v>
+        <v>0.26264999999999999</v>
       </c>
       <c r="H69">
         <v>1188</v>
@@ -18916,7 +18916,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
       <c r="G70">
-        <v>0.30730049999999998</v>
+        <v>0.26264999999999999</v>
       </c>
       <c r="H70">
         <v>1188</v>
@@ -18969,7 +18969,7 @@
         <v>2.4E-2</v>
       </c>
       <c r="G71">
-        <v>0.26512199999999997</v>
+        <v>0.2266</v>
       </c>
       <c r="H71">
         <v>1188</v>
@@ -19022,7 +19022,7 @@
         <v>0.75747865668823344</v>
       </c>
       <c r="G72">
-        <v>0.38753910000000008</v>
+        <v>0.33123000000000002</v>
       </c>
       <c r="N72" t="s">
         <v>432</v>
@@ -19063,7 +19063,7 @@
         <v>2.3813963614498546</v>
       </c>
       <c r="G73">
-        <v>0.38753910000000003</v>
+        <v>0.33123000000000002</v>
       </c>
       <c r="N73" t="s">
         <v>432</v>
@@ -19104,7 +19104,7 @@
         <v>2.8964818479978529</v>
       </c>
       <c r="G74">
-        <v>0.38753910000000003</v>
+        <v>0.33123000000000002</v>
       </c>
       <c r="N74" t="s">
         <v>432</v>
@@ -19145,7 +19145,7 @@
         <v>2.2224923223709707</v>
       </c>
       <c r="G75">
-        <v>0.38753910000000003</v>
+        <v>0.33123000000000002</v>
       </c>
       <c r="N75" t="s">
         <v>432</v>
@@ -19186,7 +19186,7 @@
         <v>0.11745081149308761</v>
       </c>
       <c r="G76">
-        <v>0.38753910000000003</v>
+        <v>0.33123000000000002</v>
       </c>
       <c r="N76" t="s">
         <v>432</v>
@@ -19227,7 +19227,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="G77">
-        <v>0.42781049999999993</v>
+        <v>0.36564999999999998</v>
       </c>
       <c r="H77">
         <v>1633.5000000000002</v>
@@ -19280,7 +19280,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="G78">
-        <v>0.42781049999999993</v>
+        <v>0.36564999999999998</v>
       </c>
       <c r="H78">
         <v>1633.5000000000002</v>
@@ -19333,7 +19333,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
       <c r="G79">
-        <v>0.39768300000000001</v>
+        <v>0.33990000000000004</v>
       </c>
       <c r="H79">
         <v>1782.0000000000002</v>
@@ -19386,7 +19386,7 @@
         <v>4.36E-2</v>
       </c>
       <c r="G80">
-        <v>0.39768299999999995</v>
+        <v>0.33990000000000004</v>
       </c>
       <c r="H80">
         <v>1782.0000000000002</v>
@@ -19439,7 +19439,7 @@
         <v>4.36E-2</v>
       </c>
       <c r="G81">
-        <v>0.39768299999999995</v>
+        <v>0.33990000000000004</v>
       </c>
       <c r="H81">
         <v>1782.0000000000002</v>
@@ -19492,7 +19492,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="G82">
-        <v>0.36152999999999996</v>
+        <v>0.309</v>
       </c>
       <c r="H82">
         <v>1782.0000000000002</v>
@@ -19545,7 +19545,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="G83">
-        <v>0.36152999999999996</v>
+        <v>0.309</v>
       </c>
       <c r="H83">
         <v>1782.0000000000002</v>
@@ -19598,7 +19598,7 @@
         <v>2.7E-2</v>
       </c>
       <c r="G84">
-        <v>0.40370850000000003</v>
+        <v>0.34505000000000002</v>
       </c>
       <c r="H84">
         <v>1782.0000000000002</v>
@@ -19651,7 +19651,7 @@
         <v>2.7E-2</v>
       </c>
       <c r="G85">
-        <v>0.40370850000000003</v>
+        <v>0.34505000000000002</v>
       </c>
       <c r="H85">
         <v>1782.0000000000002</v>
@@ -19704,7 +19704,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
       <c r="G86">
-        <v>0.39768300000000001</v>
+        <v>0.33990000000000004</v>
       </c>
       <c r="H86">
         <v>1518.0000000000002</v>
@@ -19757,7 +19757,7 @@
         <v>3.8399999999999997E-2</v>
       </c>
       <c r="G87">
-        <v>0.38563199999999997</v>
+        <v>0.3296</v>
       </c>
       <c r="H87">
         <v>1782.0000000000002</v>
@@ -19810,7 +19810,7 @@
         <v>2.4E-2</v>
       </c>
       <c r="G88">
-        <v>0.40370850000000003</v>
+        <v>0.34505000000000002</v>
       </c>
       <c r="H88">
         <v>1782.0000000000002</v>
@@ -19863,7 +19863,7 @@
         <v>2.4E-2</v>
       </c>
       <c r="G89">
-        <v>0.40370850000000003</v>
+        <v>0.34505000000000002</v>
       </c>
       <c r="H89">
         <v>1782.0000000000002</v>
@@ -19916,7 +19916,7 @@
         <v>2.0899999999999998E-2</v>
       </c>
       <c r="G90">
-        <v>0.38563199999999997</v>
+        <v>0.3296</v>
       </c>
       <c r="H90">
         <v>1782.0000000000002</v>
@@ -19969,7 +19969,7 @@
         <v>4.87E-2</v>
       </c>
       <c r="G91">
-        <v>0.39768300000000001</v>
+        <v>0.33990000000000004</v>
       </c>
       <c r="H91">
         <v>1782.0000000000005</v>
@@ -29084,7 +29084,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
       <c r="G264">
-        <v>0.57844799999999996</v>
+        <v>0.49440000000000001</v>
       </c>
       <c r="H264">
         <v>1633.5000000000002</v>
@@ -29137,7 +29137,7 @@
         <v>0.2</v>
       </c>
       <c r="G265">
-        <v>0.60255000000000003</v>
+        <v>0.51500000000000001</v>
       </c>
       <c r="H265">
         <v>1391.5</v>
@@ -29190,7 +29190,7 @@
         <v>0.2</v>
       </c>
       <c r="G266">
-        <v>0.60255000000000003</v>
+        <v>0.51500000000000001</v>
       </c>
       <c r="H266">
         <v>1391.5</v>
@@ -29243,7 +29243,7 @@
         <v>0.2</v>
       </c>
       <c r="G267">
-        <v>0.60255000000000003</v>
+        <v>0.51500000000000001</v>
       </c>
       <c r="H267">
         <v>1391.5</v>
@@ -29296,7 +29296,7 @@
         <v>6.0999999999999999E-2</v>
       </c>
       <c r="G268">
-        <v>0.60255000000000003</v>
+        <v>0.51500000000000001</v>
       </c>
       <c r="H268">
         <v>1391.5</v>
@@ -29349,7 +29349,7 @@
         <v>0.125</v>
       </c>
       <c r="G269">
-        <v>0.33742800000000001</v>
+        <v>0.28840000000000005</v>
       </c>
       <c r="H269">
         <v>1138.5</v>
@@ -29402,7 +29402,7 @@
         <v>0.125</v>
       </c>
       <c r="G270">
-        <v>0.30730049999999998</v>
+        <v>0.26264999999999999</v>
       </c>
       <c r="H270">
         <v>1138.5</v>
@@ -29455,7 +29455,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
       <c r="G271">
-        <v>0.34947899999999993</v>
+        <v>0.29869999999999997</v>
       </c>
       <c r="H271">
         <v>1336.5</v>
@@ -29508,7 +29508,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
       <c r="G272">
-        <v>0.32537699999999997</v>
+        <v>0.27810000000000001</v>
       </c>
       <c r="H272">
         <v>1336.5</v>
@@ -29561,7 +29561,7 @@
         <v>0.05</v>
       </c>
       <c r="G273">
-        <v>0.34947899999999987</v>
+        <v>0.29869999999999997</v>
       </c>
       <c r="H273">
         <v>1336.5</v>
@@ -29614,7 +29614,7 @@
         <v>0.04</v>
       </c>
       <c r="G274">
-        <v>0.32537699999999997</v>
+        <v>0.27810000000000001</v>
       </c>
       <c r="H274">
         <v>1336.5</v>
@@ -29667,7 +29667,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G275">
-        <v>0.2952495</v>
+        <v>0.25235000000000002</v>
       </c>
       <c r="H275">
         <v>1336.5</v>
@@ -29720,7 +29720,7 @@
         <v>0.02</v>
       </c>
       <c r="G276">
-        <v>0.2952495</v>
+        <v>0.25235000000000002</v>
       </c>
       <c r="H276">
         <v>1336.5</v>
@@ -29773,7 +29773,7 @@
         <v>0.02</v>
       </c>
       <c r="G277">
-        <v>0.2952495</v>
+        <v>0.25235000000000002</v>
       </c>
       <c r="H277">
         <v>1336.5</v>
@@ -29826,7 +29826,7 @@
         <v>9.1999999999999998E-2</v>
       </c>
       <c r="G278">
-        <v>0.28922399999999998</v>
+        <v>0.2472</v>
       </c>
       <c r="H278">
         <v>1138.5</v>
@@ -29879,7 +29879,7 @@
         <v>9.1999999999999998E-2</v>
       </c>
       <c r="G279">
-        <v>0.26512199999999997</v>
+        <v>0.2266</v>
       </c>
       <c r="H279">
         <v>1138.5</v>
@@ -29932,7 +29932,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="G280">
-        <v>0.28922399999999998</v>
+        <v>0.24719999999999998</v>
       </c>
       <c r="H280">
         <v>1138.5</v>
@@ -29985,7 +29985,7 @@
         <v>9.1999999999999998E-2</v>
       </c>
       <c r="G281">
-        <v>0.30730049999999998</v>
+        <v>0.26264999999999999</v>
       </c>
       <c r="H281">
         <v>1138.5</v>
@@ -30038,7 +30038,7 @@
         <v>9.1999999999999998E-2</v>
       </c>
       <c r="G282">
-        <v>0.26512199999999997</v>
+        <v>0.2266</v>
       </c>
       <c r="H282">
         <v>1138.5</v>
@@ -30091,7 +30091,7 @@
         <v>0.04</v>
       </c>
       <c r="G283">
-        <v>0.32537699999999997</v>
+        <v>0.27810000000000001</v>
       </c>
       <c r="H283">
         <v>1336.5</v>
@@ -30144,7 +30144,7 @@
         <v>0.04</v>
       </c>
       <c r="G284">
-        <v>0.32537699999999997</v>
+        <v>0.27810000000000001</v>
       </c>
       <c r="H284">
         <v>1336.5</v>
@@ -30197,7 +30197,7 @@
         <v>0.13300000000000001</v>
       </c>
       <c r="G285">
-        <v>0.37960650000000001</v>
+        <v>0.32445000000000002</v>
       </c>
       <c r="H285">
         <v>1265</v>
@@ -30250,7 +30250,7 @@
         <v>0.126</v>
       </c>
       <c r="G286">
-        <v>0.42178499999999997</v>
+        <v>0.36049999999999999</v>
       </c>
       <c r="H286">
         <v>1265</v>
@@ -30303,7 +30303,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
       <c r="G287">
-        <v>0.37960650000000001</v>
+        <v>0.32445000000000002</v>
       </c>
       <c r="H287">
         <v>1485.0000000000002</v>
@@ -30356,7 +30356,7 @@
         <v>2.2499999999999999E-2</v>
       </c>
       <c r="G288">
-        <v>0.373581</v>
+        <v>0.31930000000000003</v>
       </c>
       <c r="H288">
         <v>1930.5000000000002</v>
@@ -30409,7 +30409,7 @@
         <v>2.2499999999999999E-2</v>
       </c>
       <c r="G289">
-        <v>0.373581</v>
+        <v>0.31930000000000003</v>
       </c>
       <c r="H289">
         <v>1930.5000000000002</v>
@@ -30462,7 +30462,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
       <c r="G290">
-        <v>0.34947899999999993</v>
+        <v>0.29869999999999997</v>
       </c>
       <c r="H290">
         <v>1930.5000000000002</v>
@@ -30515,7 +30515,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
       <c r="G291">
-        <v>0.36152999999999996</v>
+        <v>0.309</v>
       </c>
       <c r="H291">
         <v>1930.5000000000005</v>
@@ -30568,7 +30568,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
       <c r="G292">
-        <v>0.3916575000000001</v>
+        <v>0.33475000000000005</v>
       </c>
       <c r="H292">
         <v>1930.5000000000007</v>
@@ -30621,7 +30621,7 @@
         <v>2.4E-2</v>
       </c>
       <c r="G293">
-        <v>0.33742800000000001</v>
+        <v>0.28840000000000005</v>
       </c>
       <c r="H293">
         <v>1930.5000000000007</v>
@@ -30674,7 +30674,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
       <c r="G294">
-        <v>0.34947899999999993</v>
+        <v>0.29869999999999997</v>
       </c>
       <c r="H294">
         <v>1930.5000000000005</v>
@@ -30727,7 +30727,7 @@
         <v>2.3E-2</v>
       </c>
       <c r="G295">
-        <v>0.34947899999999993</v>
+        <v>0.29869999999999997</v>
       </c>
       <c r="H295">
         <v>1930.5000000000002</v>
@@ -30780,7 +30780,7 @@
         <v>2.4E-2</v>
       </c>
       <c r="G296">
-        <v>0.33742800000000001</v>
+        <v>0.28840000000000005</v>
       </c>
       <c r="H296">
         <v>1930.5000000000007</v>
@@ -30801,7 +30801,7 @@
         <v>315</v>
       </c>
       <c r="P296" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q296" t="s">
         <v>434</v>
@@ -30836,7 +30836,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L297">
-        <v>0.17165578681961038</v>
+        <v>0.17165578681961036</v>
       </c>
       <c r="N297" t="s">
         <v>432</v>
@@ -30845,7 +30845,7 @@
         <v>315</v>
       </c>
       <c r="P297" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="Q297" t="s">
         <v>434</v>
@@ -30880,7 +30880,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L298">
-        <v>0.17165578681961038</v>
+        <v>0.17165578681961036</v>
       </c>
       <c r="N298" t="s">
         <v>432</v>
@@ -30924,7 +30924,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L299">
-        <v>0.17165578681961038</v>
+        <v>0.17165578681961036</v>
       </c>
       <c r="N299" t="s">
         <v>432</v>
@@ -30989,7 +30989,7 @@
         <v>321</v>
       </c>
       <c r="P300" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="Q300" t="s">
         <v>434</v>
@@ -31045,7 +31045,7 @@
         <v>321</v>
       </c>
       <c r="P301" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q301" t="s">
         <v>434</v>
@@ -31829,7 +31829,7 @@
         <v>344</v>
       </c>
       <c r="P315" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="Q315" t="s">
         <v>434</v>
@@ -31885,7 +31885,7 @@
         <v>344</v>
       </c>
       <c r="P316" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q316" t="s">
         <v>434</v>
@@ -33005,7 +33005,7 @@
         <v>375</v>
       </c>
       <c r="P336" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="Q336" t="s">
         <v>434</v>
@@ -33061,7 +33061,7 @@
         <v>375</v>
       </c>
       <c r="P337" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q337" t="s">
         <v>434</v>
@@ -33957,7 +33957,7 @@
         <v>401</v>
       </c>
       <c r="P353" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q353" t="s">
         <v>434</v>
@@ -34013,7 +34013,7 @@
         <v>401</v>
       </c>
       <c r="P354" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="Q354" t="s">
         <v>434</v>
@@ -34573,7 +34573,7 @@
         <v>413</v>
       </c>
       <c r="P364" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q364" t="s">
         <v>434</v>
@@ -34629,7 +34629,7 @@
         <v>413</v>
       </c>
       <c r="P365" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="Q365" t="s">
         <v>434</v>
@@ -34741,7 +34741,7 @@
         <v>417</v>
       </c>
       <c r="P367" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="Q367" t="s">
         <v>434</v>
@@ -34797,7 +34797,7 @@
         <v>417</v>
       </c>
       <c r="P368" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Q368" t="s">
         <v>434</v>
@@ -52611,7 +52611,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06224567-2E60-4AA1-A4B7-550548A1A895}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{859EE26B-9579-4BD3-8FFD-2DEEF07285AC}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
